--- a/nas_bench_201_experiments/gvae/training_metrics_CIFAR100.xlsx
+++ b/nas_bench_201_experiments/gvae/training_metrics_CIFAR100.xlsx
@@ -480,28 +480,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1199.516826881836</v>
+        <v>2823.831472207031</v>
       </c>
       <c r="C2" t="n">
-        <v>3.83626783543396</v>
+        <v>4.200437239547729</v>
       </c>
       <c r="D2" t="n">
-        <v>1.49437066349411</v>
+        <v>1.289183251753807</v>
       </c>
       <c r="E2" t="n">
-        <v>1195.673090206055</v>
+        <v>2819.624621195313</v>
       </c>
       <c r="F2" t="n">
-        <v>145.5999327687299</v>
+        <v>334.1497470515937</v>
       </c>
       <c r="G2" t="n">
-        <v>2.636315596924326</v>
+        <v>3.591121980626665</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4046578532642097</v>
+        <v>0.2308728866962196</v>
       </c>
       <c r="I2" t="n">
-        <v>142.9615957168654</v>
+        <v>330.5574734711141</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +509,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>56.20478612359619</v>
+        <v>136.3331529895019</v>
       </c>
       <c r="C3" t="n">
-        <v>1.924425507957459</v>
+        <v>2.88440558190918</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2966804718065262</v>
+        <v>0.1334527920622826</v>
       </c>
       <c r="E3" t="n">
-        <v>54.27887740484619</v>
+        <v>133.4480812728272</v>
       </c>
       <c r="F3" t="n">
-        <v>8.350633383870708</v>
+        <v>28.49855243863328</v>
       </c>
       <c r="G3" t="n">
-        <v>1.617665720763837</v>
+        <v>2.095168576170531</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2486812370879421</v>
+        <v>0.07489305525191652</v>
       </c>
       <c r="I3" t="n">
-        <v>6.731724274092358</v>
+        <v>26.40300942313613</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +538,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5.851788360961914</v>
+        <v>11.11326151452637</v>
       </c>
       <c r="C4" t="n">
-        <v>1.604618676948547</v>
+        <v>1.731504333274841</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4049633657112122</v>
+        <v>0.0673563093047142</v>
       </c>
       <c r="E4" t="n">
-        <v>4.245144895568847</v>
+        <v>9.381420416191101</v>
       </c>
       <c r="F4" t="n">
-        <v>1.707563461098352</v>
+        <v>3.000506308961654</v>
       </c>
       <c r="G4" t="n">
-        <v>1.597550451448263</v>
+        <v>1.608965105885977</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5443004809273787</v>
+        <v>0.07827831959257701</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1072915085654274</v>
+        <v>1.391149845940059</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +567,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.072931453544617</v>
+        <v>2.378427482421875</v>
       </c>
       <c r="C5" t="n">
-        <v>1.57970537046051</v>
+        <v>1.602595519241333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5133521132011414</v>
+        <v>0.1196245695533752</v>
       </c>
       <c r="E5" t="n">
-        <v>2.490659363098144</v>
+        <v>0.7752338457717896</v>
       </c>
       <c r="F5" t="n">
-        <v>3.259067267407017</v>
+        <v>1.60788379045334</v>
       </c>
       <c r="G5" t="n">
-        <v>1.553280898066174</v>
+        <v>1.591402086060354</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4807317608196234</v>
+        <v>0.1347182757216605</v>
       </c>
       <c r="I5" t="n">
-        <v>1.703382724035428</v>
+        <v>0.01580812059488713</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +596,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.402882709083557</v>
+        <v>2.190252835601807</v>
       </c>
       <c r="C6" t="n">
-        <v>1.489181980369568</v>
+        <v>1.55515092829895</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4571932786865234</v>
+        <v>0.1408911270904541</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9114147774705886</v>
+        <v>0.6343974646606445</v>
       </c>
       <c r="F6" t="n">
-        <v>1.549675337245375</v>
+        <v>1.504960399459665</v>
       </c>
       <c r="G6" t="n">
-        <v>1.400802170254083</v>
+        <v>1.493686964609106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5534070378804479</v>
+        <v>0.1548155156560668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1461061650232623</v>
+        <v>0.01049934171881606</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +625,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.645601290206909</v>
+        <v>1.860469316833496</v>
       </c>
       <c r="C7" t="n">
-        <v>1.359999874023438</v>
+        <v>1.425403884040833</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6254847955093383</v>
+        <v>0.2456342075138092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2824739988276959</v>
+        <v>0.4338372857971192</v>
       </c>
       <c r="F7" t="n">
-        <v>1.656378573165632</v>
+        <v>1.333141536549293</v>
       </c>
       <c r="G7" t="n">
-        <v>1.270041184767619</v>
+        <v>1.315613512176091</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6316796538608109</v>
+        <v>0.3108214243376236</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3831789946614432</v>
+        <v>0.01597390869605016</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +654,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.375795854148865</v>
+        <v>1.444044005737305</v>
       </c>
       <c r="C8" t="n">
-        <v>1.227218045883179</v>
+        <v>1.290214035362244</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6503081535720825</v>
+        <v>0.3742789570198059</v>
       </c>
       <c r="E8" t="n">
-        <v>0.145326266348958</v>
+        <v>0.1519585793571472</v>
       </c>
       <c r="F8" t="n">
-        <v>1.669821321532543</v>
+        <v>1.231292856124641</v>
       </c>
       <c r="G8" t="n">
-        <v>1.267024180076251</v>
+        <v>1.202857811221485</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7348451417616491</v>
+        <v>0.415603242622503</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3991228933104878</v>
+        <v>0.02635701562777818</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +683,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.212745752052307</v>
+        <v>1.262013656829834</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0804978748703</v>
+        <v>1.149282420280457</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7021605092163086</v>
+        <v>0.4376655402126312</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1287370687837601</v>
+        <v>0.1105428987388611</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9845396254229896</v>
+        <v>1.034821034146755</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9606907076781181</v>
+        <v>1.008842502037036</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6708011532957753</v>
+        <v>0.4432054366275887</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02049491551192705</v>
+        <v>0.02376249770319384</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +712,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.004949386787415</v>
+        <v>1.07208435552597</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9146498402786255</v>
+        <v>0.9758548676261902</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7500869170036316</v>
+        <v>0.500390421546936</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08654911140739918</v>
+        <v>0.09372753664016724</v>
       </c>
       <c r="F10" t="n">
-        <v>1.119851012354379</v>
+        <v>1.044705243017312</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8876887714493333</v>
+        <v>0.8211286711342767</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7935748190008602</v>
+        <v>0.4997617116487824</v>
       </c>
       <c r="I10" t="n">
-        <v>0.228194368050888</v>
+        <v>0.2210777586883277</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +741,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8424361899490357</v>
+        <v>0.9089480242767334</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7487634750595092</v>
+        <v>0.8091470695953369</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8997913692016601</v>
+        <v>0.6187610917243958</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0891737559337616</v>
+        <v>0.09670714967155457</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6011505706625312</v>
+        <v>0.7185610820690921</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5480311361728252</v>
+        <v>0.6907690124332807</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9904004878904458</v>
+        <v>0.662805416012277</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04816744597151656</v>
+        <v>0.02447803693776418</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +770,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6292533992710113</v>
+        <v>0.7541844331092834</v>
       </c>
       <c r="C12" t="n">
-        <v>0.562060335823059</v>
+        <v>0.6646754720802307</v>
       </c>
       <c r="D12" t="n">
-        <v>1.003377918266296</v>
+        <v>0.7431077458381653</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06217616955780983</v>
+        <v>0.0857934213989973</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6346170795450008</v>
+        <v>0.7812915859525783</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5669257557606036</v>
+        <v>0.6854293428276336</v>
       </c>
       <c r="H12" t="n">
-        <v>1.070840345479147</v>
+        <v>0.7965604362091077</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0623371228308312</v>
+        <v>0.09187944909682282</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +799,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5206958304519653</v>
+        <v>0.6378529759178162</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4381940253353119</v>
+        <v>0.540537136920929</v>
       </c>
       <c r="D13" t="n">
-        <v>1.124382415290833</v>
+        <v>0.8413069972839355</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07687989445018768</v>
+        <v>0.09310930260467529</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3904915576093932</v>
+        <v>0.4270048727296888</v>
       </c>
       <c r="G13" t="n">
-        <v>0.350071688456792</v>
+        <v>0.3868787788314104</v>
       </c>
       <c r="H13" t="n">
-        <v>1.243849309490322</v>
+        <v>0.9471661966776576</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03420062621159033</v>
+        <v>0.03539026337020938</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +828,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4340225897483826</v>
+        <v>0.5111586552600861</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3470262823810578</v>
+        <v>0.4147199499855042</v>
       </c>
       <c r="D14" t="n">
-        <v>1.260855984443665</v>
+        <v>0.9606631313285827</v>
       </c>
       <c r="E14" t="n">
-        <v>0.08069202782428264</v>
+        <v>0.09163538928949833</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5509784520975334</v>
+        <v>0.6378216974886946</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4852973966186237</v>
+        <v>0.463230922436053</v>
       </c>
       <c r="H14" t="n">
-        <v>1.357117761375465</v>
+        <v>1.061816507350368</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05889546139934518</v>
+        <v>0.1692816954287191</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +857,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3665420459537506</v>
+        <v>0.4434493883743286</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2841896054611206</v>
+        <v>0.3375651040840149</v>
       </c>
       <c r="D15" t="n">
-        <v>1.321821762504578</v>
+        <v>1.063886106422424</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0757433328576088</v>
+        <v>0.1005648559536934</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2348803873348003</v>
+        <v>0.2970396549608346</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1947343774506941</v>
+        <v>0.2565136366081082</v>
       </c>
       <c r="H15" t="n">
-        <v>1.313828376043485</v>
+        <v>1.110484560434425</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03357687014351078</v>
+        <v>0.03497359392450451</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +886,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3053935580062866</v>
+        <v>0.3523422176065445</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2352563463859558</v>
+        <v>0.2668010215654373</v>
       </c>
       <c r="D16" t="n">
-        <v>1.30351503289032</v>
+        <v>1.109457207244873</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0636196359500885</v>
+        <v>0.07999391280424595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3959121270553128</v>
+        <v>0.4288753327615498</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2929080089484303</v>
+        <v>0.2571990973389363</v>
       </c>
       <c r="H16" t="n">
-        <v>1.35853119451109</v>
+        <v>1.109032281382438</v>
       </c>
       <c r="I16" t="n">
-        <v>0.096211462278545</v>
+        <v>0.1661310670095789</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +915,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2696246715297699</v>
+        <v>0.3137546728134155</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2021239447727203</v>
+        <v>0.2298545350847244</v>
       </c>
       <c r="D17" t="n">
-        <v>1.302767988845825</v>
+        <v>1.132411586715698</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06098688899469375</v>
+        <v>0.07823808079147339</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1906842682684421</v>
+        <v>0.2295105559265828</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1571828968489928</v>
+        <v>0.1892052873128001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.362782433176896</v>
+        <v>1.135151704606185</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02668745962711474</v>
+        <v>0.03462950847544639</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +944,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.2330971242179871</v>
+        <v>0.2634092063064575</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1706529980134964</v>
+        <v>0.1930277275295258</v>
       </c>
       <c r="D18" t="n">
-        <v>1.268071999771118</v>
+        <v>1.121245242477417</v>
       </c>
       <c r="E18" t="n">
-        <v>0.05610376491260528</v>
+        <v>0.06477525283908844</v>
       </c>
       <c r="F18" t="n">
-        <v>0.291439132359833</v>
+        <v>0.3282716417604325</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2012510079476028</v>
+        <v>0.2225050869841755</v>
       </c>
       <c r="H18" t="n">
-        <v>1.297703568075843</v>
+        <v>1.111857123102683</v>
       </c>
       <c r="I18" t="n">
-        <v>0.08369960865033198</v>
+        <v>0.1002072710007867</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +973,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1930041524276734</v>
+        <v>0.2304848107337952</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1407519608373642</v>
+        <v>0.1675780304851532</v>
       </c>
       <c r="D19" t="n">
-        <v>1.210629898872376</v>
+        <v>1.095293945037842</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04619904130840301</v>
+        <v>0.05743030902481079</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1310226221788571</v>
+        <v>0.1529638541960211</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1061578502322488</v>
+        <v>0.1215211415179013</v>
       </c>
       <c r="H19" t="n">
-        <v>1.175576068627698</v>
+        <v>1.121216577519017</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01898689224489556</v>
+        <v>0.0258366308993315</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +1002,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1613119340314865</v>
+        <v>0.1960486516256332</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1152767584581375</v>
+        <v>0.1434463472986221</v>
       </c>
       <c r="D20" t="n">
-        <v>1.176785450325012</v>
+        <v>1.070899896827698</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04015124877250194</v>
+        <v>0.0472478059155941</v>
       </c>
       <c r="F20" t="n">
-        <v>0.154829994302006</v>
+        <v>0.2283788894634651</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07399462753806574</v>
+        <v>0.1487823074210137</v>
       </c>
       <c r="H20" t="n">
-        <v>1.202301913762365</v>
+        <v>1.016166630257985</v>
       </c>
       <c r="I20" t="n">
-        <v>0.07482385794888896</v>
+        <v>0.07451575414537411</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1031,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1328528978223801</v>
+        <v>0.1689448706941604</v>
       </c>
       <c r="C21" t="n">
-        <v>0.08946837429618835</v>
+        <v>0.1224476181745529</v>
       </c>
       <c r="D21" t="n">
-        <v>1.147594959625244</v>
+        <v>1.028974557907105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03764654981446266</v>
+        <v>0.04135237921094895</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1136441885204727</v>
+        <v>0.1294970434797141</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07214909118306967</v>
+        <v>0.1031762324562858</v>
       </c>
       <c r="H21" t="n">
-        <v>1.133052546546276</v>
+        <v>1.076261704874272</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03582983629106503</v>
+        <v>0.02093950082351975</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1060,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1111096383275986</v>
+        <v>0.1429068900403976</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07133940499687196</v>
+        <v>0.09964253010749817</v>
       </c>
       <c r="D22" t="n">
-        <v>1.116211210800171</v>
+        <v>0.9976943092575074</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03418917666339874</v>
+        <v>0.03827588865303994</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1027157761897971</v>
+        <v>0.1593244346378289</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0525514395401295</v>
+        <v>0.1106991663011213</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9876354815909368</v>
+        <v>1.050317903272868</v>
       </c>
       <c r="I22" t="n">
-        <v>0.04522615967236374</v>
+        <v>0.04337367816957331</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1089,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.09192444296598434</v>
+        <v>0.1217016567511559</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05771817100286484</v>
+        <v>0.0811133774163723</v>
       </c>
       <c r="D23" t="n">
-        <v>1.038843135047913</v>
+        <v>0.9785337161903381</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02901205655300617</v>
+        <v>0.03569561108350754</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1070647721340178</v>
+        <v>0.1176217202582134</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03750302473930901</v>
+        <v>0.06901569833422952</v>
       </c>
       <c r="H23" t="n">
-        <v>1.29952879010367</v>
+        <v>1.008160137733472</v>
       </c>
       <c r="I23" t="n">
-        <v>0.06306410413727674</v>
+        <v>0.04356522216128875</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1118,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.08056431475162507</v>
+        <v>0.1037935389347076</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04495763244247437</v>
+        <v>0.06681642267680168</v>
       </c>
       <c r="D24" t="n">
-        <v>1.023089231143951</v>
+        <v>0.9562347242202759</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0304912366566658</v>
+        <v>0.03219594268107414</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06999636150738543</v>
+        <v>0.1448547933696728</v>
       </c>
       <c r="G24" t="n">
-        <v>0.04747385489050949</v>
+        <v>0.05079722168978431</v>
       </c>
       <c r="H24" t="n">
-        <v>1.078532600791769</v>
+        <v>0.7950132050872043</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01712984426849526</v>
+        <v>0.09008250295970023</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1147,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.06780438665676117</v>
+        <v>0.0934938190073967</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03333951810574531</v>
+        <v>0.05341272453093529</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9808879861717225</v>
+        <v>0.9356547031135559</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02956042927193642</v>
+        <v>0.03540282093238831</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1450013072270943</v>
+        <v>0.08194781567785907</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03181297703264783</v>
+        <v>0.04879462932563139</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7846608232673968</v>
+        <v>0.8895826252210782</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1092650261681776</v>
+        <v>0.02870527376431431</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1176,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.05699802637100219</v>
+        <v>0.07861991003322601</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02571130918943882</v>
+        <v>0.04297975336408615</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9192814646682739</v>
+        <v>0.9106100996170043</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02669030934429169</v>
+        <v>0.03108710675692558</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05167063261906436</v>
+        <v>0.09773266783060101</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02973447892346934</v>
+        <v>0.03575377845538091</v>
       </c>
       <c r="H26" t="n">
-        <v>1.001747529611696</v>
+        <v>0.854586891474576</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01692741572431503</v>
+        <v>0.05770595486654154</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1205,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.05032555632853508</v>
+        <v>0.06973869819450379</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02171310664689541</v>
+        <v>0.03737763701105118</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8744088632926941</v>
+        <v>0.8664633512878418</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02424040575122833</v>
+        <v>0.02802874381530285</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04194756741527632</v>
+        <v>0.05394041924453287</v>
       </c>
       <c r="G27" t="n">
-        <v>0.017672836515463</v>
+        <v>0.03129926930705836</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8821991089623281</v>
+        <v>0.8282775893413612</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0198637356798713</v>
+        <v>0.01849976228510575</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1234,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04734930320286751</v>
+        <v>0.05995791463851929</v>
       </c>
       <c r="C28" t="n">
-        <v>0.01893636721217632</v>
+        <v>0.02939530542135239</v>
       </c>
       <c r="D28" t="n">
-        <v>0.813605883934021</v>
+        <v>0.8265423156166076</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02434490671920776</v>
+        <v>0.02642989765298366</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03386548396643573</v>
+        <v>0.1138256253032272</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01055796910940288</v>
+        <v>0.0267613254908053</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7912055787526764</v>
+        <v>0.7072276571174235</v>
       </c>
       <c r="I28" t="n">
-        <v>0.01935148696368029</v>
+        <v>0.08352816176113063</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1263,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0381006778473854</v>
+        <v>0.05658485310649872</v>
       </c>
       <c r="C29" t="n">
-        <v>0.01292927699330449</v>
+        <v>0.02832989903020859</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7437007703933716</v>
+        <v>0.7844285820922852</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02145289710235596</v>
+        <v>0.02433281085717678</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04007021796669306</v>
+        <v>0.06444731076477403</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007800281142320661</v>
+        <v>0.04570915978796914</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7244646285525348</v>
+        <v>0.7674344544620731</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02864761347422106</v>
+        <v>0.01490097893885113</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1292,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.03459740130877495</v>
+        <v>0.04742336725950241</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01077869564972818</v>
+        <v>0.02088419553053379</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6952098322486877</v>
+        <v>0.7551494491882325</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02034265666222572</v>
+        <v>0.02276342485833168</v>
       </c>
       <c r="F30" t="n">
-        <v>0.03463934529007551</v>
+        <v>0.05576467168904829</v>
       </c>
       <c r="G30" t="n">
-        <v>0.008378471823570243</v>
+        <v>0.01571901811830712</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6571986539873369</v>
+        <v>0.6648696698100104</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0229748808813766</v>
+        <v>0.03672130521222779</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1321,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.02898849282181263</v>
+        <v>0.04258794834256172</v>
       </c>
       <c r="C31" t="n">
-        <v>0.00941837832581997</v>
+        <v>0.01468406125879288</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6260809178657532</v>
+        <v>0.7058942723503113</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01643971006527543</v>
+        <v>0.02437441587084532</v>
       </c>
       <c r="F31" t="n">
-        <v>0.03024641234980711</v>
+        <v>0.04056802317961977</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01481862228084204</v>
+        <v>0.02326722051042814</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6006575618988149</v>
+        <v>0.7140337734004607</v>
       </c>
       <c r="I31" t="n">
-        <v>0.01242450227107105</v>
+        <v>0.01373063373703017</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1350,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.02596646607339382</v>
+        <v>0.03698773068594933</v>
       </c>
       <c r="C32" t="n">
-        <v>0.006541823807775974</v>
+        <v>0.01305387603747845</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5934613059501648</v>
+        <v>0.6606725317687988</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01645733579182625</v>
+        <v>0.02063049172604084</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03525550181650804</v>
+        <v>0.024686583428238</v>
       </c>
       <c r="G32" t="n">
-        <v>0.004490508802879304</v>
+        <v>0.009063547344279718</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5263336282764329</v>
+        <v>0.654960338544301</v>
       </c>
       <c r="I32" t="n">
-        <v>0.02813332522698172</v>
+        <v>0.01234823438802318</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1379,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.02359665166532993</v>
+        <v>0.03407481569296122</v>
       </c>
       <c r="C33" t="n">
-        <v>0.00378109912019223</v>
+        <v>0.01362671785491705</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5445570464172363</v>
+        <v>0.6186830146865845</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01709276737779379</v>
+        <v>0.01735468274307251</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0216864979651196</v>
+        <v>0.01463250364603848</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002655308383576219</v>
+        <v>0.003870500628646542</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5212250241136474</v>
+        <v>0.6055820755118453</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01642506464550099</v>
+        <v>0.007734092871246778</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1408,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.02321196245932579</v>
+        <v>0.02818379060387611</v>
       </c>
       <c r="C34" t="n">
-        <v>0.007159977238535881</v>
+        <v>0.008603513243794441</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4906484338302612</v>
+        <v>0.5697546054420471</v>
       </c>
       <c r="E34" t="n">
-        <v>0.01359874289786816</v>
+        <v>0.01673150462865829</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1109501372576732</v>
+        <v>0.06370773358407261</v>
       </c>
       <c r="G34" t="n">
-        <v>0.09907883014706181</v>
+        <v>0.04862103506995648</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4846339268124317</v>
+        <v>0.5326862351307083</v>
       </c>
       <c r="I34" t="n">
-        <v>0.009448138421574581</v>
+        <v>0.01242326758267148</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1437,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.02442040932536125</v>
+        <v>0.02491634977865219</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01107235880360752</v>
+        <v>0.006971001088678837</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4405472444725037</v>
+        <v>0.5245608768806458</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01114531450128555</v>
+        <v>0.01532254455161095</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0214458668526098</v>
+        <v>0.03545114966385905</v>
       </c>
       <c r="G35" t="n">
-        <v>0.002278430785795409</v>
+        <v>0.005558281291525379</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4409087826104965</v>
+        <v>0.5038708675666113</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0169628918615776</v>
+        <v>0.02737351391118074</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1466,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01868631914615631</v>
+        <v>0.0233271961054802</v>
       </c>
       <c r="C36" t="n">
-        <v>0.00529902738840133</v>
+        <v>0.005174440927013755</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4224232031059265</v>
+        <v>0.4948327549800873</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01127517591145635</v>
+        <v>0.01567859131616354</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01193354904092545</v>
+        <v>0.02399234584285034</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0005422253280932761</v>
+        <v>0.003295841217527187</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3829292232819133</v>
+        <v>0.5019420285248251</v>
       </c>
       <c r="I36" t="n">
-        <v>0.009476677669336804</v>
+        <v>0.01818679454908091</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1495,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.01709333903634548</v>
+        <v>0.02141686480307579</v>
       </c>
       <c r="C37" t="n">
-        <v>0.004308110406160355</v>
+        <v>0.006644953028187156</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3911746984329224</v>
+        <v>0.4555448865184784</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01082935503125191</v>
+        <v>0.01249418722140789</v>
       </c>
       <c r="F37" t="n">
-        <v>0.009797455428523691</v>
+        <v>0.01924267512307081</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0004768214499893892</v>
+        <v>0.003783025749842067</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3700580780132754</v>
+        <v>0.4157003720549541</v>
       </c>
       <c r="I37" t="n">
-        <v>0.007470343696169227</v>
+        <v>0.01338114746285642</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1524,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.01530158981639147</v>
+        <v>0.02010195233076811</v>
       </c>
       <c r="C38" t="n">
-        <v>0.005859210749611259</v>
+        <v>0.006875580950841308</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3617800401611328</v>
+        <v>0.4263746406459809</v>
       </c>
       <c r="E38" t="n">
-        <v>0.007633478832304478</v>
+        <v>0.01109449805295467</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01240872803601462</v>
+        <v>0.01467232600838967</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0008838350712519206</v>
+        <v>0.0008629960697759581</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3546003601893321</v>
+        <v>0.391652551179609</v>
       </c>
       <c r="I38" t="n">
-        <v>0.009751891226949836</v>
+        <v>0.01185106714139123</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1553,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.01280571571481228</v>
+        <v>0.01699341064959764</v>
       </c>
       <c r="C39" t="n">
-        <v>0.001461963049024344</v>
+        <v>0.002312281758204103</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3467011422863007</v>
+        <v>0.3945692188587189</v>
       </c>
       <c r="E39" t="n">
-        <v>0.009610246982753277</v>
+        <v>0.01270828284615278</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01642421772973961</v>
+        <v>0.01919252083033664</v>
       </c>
       <c r="G39" t="n">
-        <v>0.001649695352292627</v>
+        <v>0.003540354097143521</v>
       </c>
       <c r="H39" t="n">
-        <v>0.3687173709531009</v>
+        <v>0.3815551291787799</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01293093538084971</v>
+        <v>0.01374439119545175</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1582,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.01285163054943085</v>
+        <v>0.01664283521008492</v>
       </c>
       <c r="C40" t="n">
-        <v>0.001459635578870773</v>
+        <v>0.004347185778908432</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3398163058738708</v>
+        <v>0.366697492319107</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0096929134670794</v>
+        <v>0.01046216204857826</v>
       </c>
       <c r="F40" t="n">
-        <v>0.04820373950298226</v>
+        <v>0.01921805489595621</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03976448625933871</v>
+        <v>0.001972737440635826</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3464578802356129</v>
+        <v>0.3554114771531029</v>
       </c>
       <c r="I40" t="n">
-        <v>0.006706963513155892</v>
+        <v>0.01546826028853023</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1611,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.01292378273028135</v>
+        <v>0.01518195726162195</v>
       </c>
       <c r="C41" t="n">
-        <v>0.003250914443627</v>
+        <v>0.003371516592316329</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3182480419521332</v>
+        <v>0.3471980907020569</v>
       </c>
       <c r="E41" t="n">
-        <v>0.008081628285467624</v>
+        <v>0.01007445027911663</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01492474949780432</v>
+        <v>0.01461238899175533</v>
       </c>
       <c r="G41" t="n">
-        <v>0.001105869826344168</v>
+        <v>0.0004586747078548625</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3128478909122224</v>
+        <v>0.3370670189281856</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01225464033196888</v>
+        <v>0.01246837943014469</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1640,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01114165184515715</v>
+        <v>0.01316228993034363</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0009027569199949503</v>
+        <v>0.002906738192915917</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3057758946743012</v>
+        <v>0.3162776539134979</v>
       </c>
       <c r="E42" t="n">
-        <v>0.00871001544624567</v>
+        <v>0.008674163640797138</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01534868321170329</v>
+        <v>0.01729645665716775</v>
       </c>
       <c r="G42" t="n">
-        <v>0.001243514635677633</v>
+        <v>0.002566722132095408</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2985598741658944</v>
+        <v>0.301320136954695</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01261236907279219</v>
+        <v>0.01322313373005944</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1669,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.01204462965512276</v>
+        <v>0.01203297882664204</v>
       </c>
       <c r="C43" t="n">
-        <v>0.003263307224178687</v>
+        <v>0.001274949941277504</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2888133875560761</v>
+        <v>0.2983081737937927</v>
       </c>
       <c r="E43" t="n">
-        <v>0.007337255609512329</v>
+        <v>0.009266488093376159</v>
       </c>
       <c r="F43" t="n">
-        <v>0.01120800585308238</v>
+        <v>0.01377754845612395</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0004848680528508253</v>
+        <v>0.001098197363985499</v>
       </c>
       <c r="H43" t="n">
-        <v>0.282668212996416</v>
+        <v>0.3050001865401742</v>
       </c>
       <c r="I43" t="n">
-        <v>0.00930979663892049</v>
+        <v>0.01115435020885693</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1698,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.01212414909350872</v>
+        <v>0.0136229320165515</v>
       </c>
       <c r="C44" t="n">
-        <v>0.004330741241348907</v>
+        <v>0.005602824291601777</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2691849269733429</v>
+        <v>0.2857075010356903</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006447483371198178</v>
+        <v>0.006591570254892111</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0129420689437508</v>
+        <v>0.01396071176185937</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0007283270497826121</v>
+        <v>0.0005412167114954667</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2534647238487909</v>
+        <v>0.257686210664606</v>
       </c>
       <c r="I44" t="n">
-        <v>0.01094641833063245</v>
+        <v>0.01213106393485921</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1727,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.01122950502878427</v>
+        <v>0.01021152205276489</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003791050291527063</v>
+        <v>0.001100438117697835</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2515793852262497</v>
+        <v>0.2699918291244507</v>
       </c>
       <c r="E45" t="n">
-        <v>0.006180557767271996</v>
+        <v>0.007761124948710204</v>
       </c>
       <c r="F45" t="n">
-        <v>0.014907598379653</v>
+        <v>0.01417571697013413</v>
       </c>
       <c r="G45" t="n">
-        <v>0.00100177793388694</v>
+        <v>0.0007419748021955154</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2441038991790417</v>
+        <v>0.2507330818316287</v>
       </c>
       <c r="I45" t="n">
-        <v>0.01268530096706811</v>
+        <v>0.01218007684246216</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1756,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.01099621328529716</v>
+        <v>0.01069484763762355</v>
       </c>
       <c r="C46" t="n">
-        <v>0.004132735546395183</v>
+        <v>0.002677461994724348</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2389443365287781</v>
+        <v>0.258668143119812</v>
       </c>
       <c r="E46" t="n">
-        <v>0.005668756052106619</v>
+        <v>0.006724045005083084</v>
       </c>
       <c r="F46" t="n">
-        <v>0.00941933845253403</v>
+        <v>0.009725547226398065</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0003450328392013877</v>
+        <v>0.0004613383337293203</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2246312818101335</v>
+        <v>0.2461785727097588</v>
       </c>
       <c r="I46" t="n">
-        <v>0.007951149186438487</v>
+        <v>0.008033316076853196</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1785,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.01052284987542033</v>
+        <v>0.009110593363881111</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00382848396060802</v>
+        <v>0.0007729271977096796</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2258501113567352</v>
+        <v>0.2441322881088257</v>
       </c>
       <c r="E47" t="n">
-        <v>0.005565115388035774</v>
+        <v>0.007117004796087741</v>
       </c>
       <c r="F47" t="n">
-        <v>0.01597266193740617</v>
+        <v>0.01302529889938298</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0006552045188576809</v>
+        <v>0.001258042929390199</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2368923378282426</v>
+        <v>0.2344352169740842</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01413299573466887</v>
+        <v>0.01059507987712667</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1814,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.007733752214491367</v>
+        <v>0.01035000863289833</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0005891352878231556</v>
+        <v>0.003889512192882597</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2290226838197708</v>
+        <v>0.2349815315628052</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005999503604501486</v>
+        <v>0.005285588779419661</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01053748687525655</v>
+        <v>0.01099290548089958</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0005739934195051818</v>
+        <v>0.000621348287196918</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2204287983076024</v>
+        <v>0.213825761093401</v>
       </c>
       <c r="I48" t="n">
-        <v>0.008861349547072199</v>
+        <v>0.009302428286540858</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1843,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.00781177932959795</v>
+        <v>0.00809623238146305</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0005074197937138379</v>
+        <v>0.0006857707471102476</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2265860756187439</v>
+        <v>0.226989777973175</v>
       </c>
       <c r="E49" t="n">
-        <v>0.006171429237812757</v>
+        <v>0.00627551271507144</v>
       </c>
       <c r="F49" t="n">
-        <v>0.008640016957898709</v>
+        <v>0.01166781967423771</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0003109063637909308</v>
+        <v>0.00056783316914846</v>
       </c>
       <c r="H49" t="n">
-        <v>0.231981585279569</v>
+        <v>0.2216215119519397</v>
       </c>
       <c r="I49" t="n">
-        <v>0.00716920276824233</v>
+        <v>0.009991878988996124</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1872,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.007147557741135359</v>
+        <v>0.01078163509398699</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0004497301250817254</v>
+        <v>0.00464798437255621</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2172259017868042</v>
+        <v>0.2247050870380402</v>
       </c>
       <c r="E50" t="n">
-        <v>0.005611698136359453</v>
+        <v>0.005010125264763832</v>
       </c>
       <c r="F50" t="n">
-        <v>0.009352409774847754</v>
+        <v>0.005610549033514632</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0004570978148620071</v>
+        <v>0.0001676081100808833</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2083837266088893</v>
+        <v>0.2132543696023123</v>
       </c>
       <c r="I50" t="n">
-        <v>0.007853393353290892</v>
+        <v>0.004376669202947938</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1901,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.006764596216320992</v>
+        <v>0.006577109514862299</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0004631795503906906</v>
+        <v>0.0004866449441742152</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2124980987329483</v>
+        <v>0.2072367310934067</v>
       </c>
       <c r="E51" t="n">
-        <v>0.005238926200151444</v>
+        <v>0.005054280953943729</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01142850438202769</v>
+        <v>0.009856045249588241</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0006931235486615699</v>
+        <v>0.000356297645490726</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2312563391484405</v>
+        <v>0.2091851209903814</v>
       </c>
       <c r="I51" t="n">
-        <v>0.00957909918239805</v>
+        <v>0.008453822060933315</v>
       </c>
     </row>
     <row r="52">
@@ -1930,28 +1930,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0.006384166020929814</v>
+        <v>0.006978475264638662</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0004517074252478778</v>
+        <v>0.0005570907405950129</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2093386372709274</v>
+        <v>0.2069631352233887</v>
       </c>
       <c r="E52" t="n">
-        <v>0.004885765434384346</v>
+        <v>0.005386568832695484</v>
       </c>
       <c r="F52" t="n">
-        <v>0.008924232165756078</v>
+        <v>0.01078416080978284</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0004247842694622834</v>
+        <v>0.0006683765959258983</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2039601637916503</v>
+        <v>0.2125172112427567</v>
       </c>
       <c r="I52" t="n">
-        <v>0.007479647107203575</v>
+        <v>0.009053198322836084</v>
       </c>
     </row>
     <row r="53">
@@ -1959,28 +1959,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.00610864490956068</v>
+        <v>0.006584051635503769</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0004983858456462622</v>
+        <v>0.0004603978537712246</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2037264189682007</v>
+        <v>0.1995853633861542</v>
       </c>
       <c r="E53" t="n">
-        <v>0.004591626948237419</v>
+        <v>0.005125727008283138</v>
       </c>
       <c r="F53" t="n">
-        <v>0.008289428878253475</v>
+        <v>0.01121574261996038</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0003484059680237315</v>
+        <v>0.001059667822011544</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2080450182103022</v>
+        <v>0.195870042688306</v>
       </c>
       <c r="I53" t="n">
-        <v>0.006900797842061344</v>
+        <v>0.009176724673374928</v>
       </c>
     </row>
     <row r="54">
@@ -1988,28 +1988,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.006004030407845974</v>
+        <v>0.006581348103582859</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0003912428428009152</v>
+        <v>0.0004650786475185305</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2030622060537338</v>
+        <v>0.1958625860519409</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00459747657430172</v>
+        <v>0.005136956523299217</v>
       </c>
       <c r="F54" t="n">
-        <v>0.01117343885887894</v>
+        <v>0.006521580719721745</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0004606703476415154</v>
+        <v>0.0003362615968079456</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1939893859654033</v>
+        <v>0.1957797720167804</v>
       </c>
       <c r="I54" t="n">
-        <v>0.00974282161142756</v>
+        <v>0.005206420215281246</v>
       </c>
     </row>
     <row r="55">
@@ -2017,28 +2017,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.007130011911898851</v>
+        <v>0.006141603769540787</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00236750592862349</v>
+        <v>0.0004307947959005833</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1973464375514984</v>
+        <v>0.1904445061368942</v>
       </c>
       <c r="E55" t="n">
-        <v>0.003775773956984281</v>
+        <v>0.004758586481422186</v>
       </c>
       <c r="F55" t="n">
-        <v>0.008956194648467503</v>
+        <v>0.01082325667142868</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0003535851389895152</v>
+        <v>0.001003293924764419</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1815440917958249</v>
+        <v>0.1895868269294549</v>
       </c>
       <c r="I55" t="n">
-        <v>0.007694889114984291</v>
+        <v>0.008872028620849815</v>
       </c>
     </row>
     <row r="56">
@@ -2046,28 +2046,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.005634606127202511</v>
+        <v>0.005847995692372322</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0003799764393083751</v>
+        <v>0.000525326614703983</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1887043793478012</v>
+        <v>0.1917978812494278</v>
       </c>
       <c r="E56" t="n">
-        <v>0.004311107833087444</v>
+        <v>0.004363679699212313</v>
       </c>
       <c r="F56" t="n">
-        <v>0.00778952162445418</v>
+        <v>0.01014719050043364</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0003003586636234051</v>
+        <v>0.0004798985710371358</v>
       </c>
       <c r="H56" t="n">
-        <v>0.192216359500395</v>
+        <v>0.191693559689584</v>
       </c>
       <c r="I56" t="n">
-        <v>0.006528081165818075</v>
+        <v>0.008708824171437039</v>
       </c>
     </row>
     <row r="57">
@@ -2075,28 +2075,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.005488837851941586</v>
+        <v>0.005870537695467472</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0003576554547827691</v>
+        <v>0.000415610933098942</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1907792997341156</v>
+        <v>0.1886838661499023</v>
       </c>
       <c r="E57" t="n">
-        <v>0.004177285888940096</v>
+        <v>0.004511507462278008</v>
       </c>
       <c r="F57" t="n">
-        <v>0.009358641025268429</v>
+        <v>0.009833903811069822</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0003180443397593999</v>
+        <v>0.0002845285133535398</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1816862716283923</v>
+        <v>0.1835206443042195</v>
       </c>
       <c r="I57" t="n">
-        <v>0.008132165257939021</v>
+        <v>0.008631772248721628</v>
       </c>
     </row>
     <row r="58">
@@ -2104,28 +2104,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0070302470408082</v>
+        <v>0.005965397865831852</v>
       </c>
       <c r="C58" t="n">
-        <v>0.002756372630503029</v>
+        <v>0.001426244352251291</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1885225417776108</v>
+        <v>0.1851350323619843</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003331261669397354</v>
+        <v>0.003613478376984596</v>
       </c>
       <c r="F58" t="n">
-        <v>0.008776007661714444</v>
+        <v>0.009130253664310566</v>
       </c>
       <c r="G58" t="n">
-        <v>0.001295441002197576</v>
+        <v>0.0006467432665128145</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1934588812401011</v>
+        <v>0.1873338404847203</v>
       </c>
       <c r="I58" t="n">
-        <v>0.006513272328317457</v>
+        <v>0.007546841260744639</v>
       </c>
     </row>
     <row r="59">
@@ -2133,28 +2133,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.007141430189609528</v>
+        <v>0.005298903585910797</v>
       </c>
       <c r="C59" t="n">
-        <v>0.003029690345432609</v>
+        <v>0.0003558136443030089</v>
       </c>
       <c r="D59" t="n">
-        <v>0.185706727517128</v>
+        <v>0.1798485373268127</v>
       </c>
       <c r="E59" t="n">
-        <v>0.003183206249028444</v>
+        <v>0.004043847291707993</v>
       </c>
       <c r="F59" t="n">
-        <v>0.009164863872914583</v>
+        <v>0.006316265589747499</v>
       </c>
       <c r="G59" t="n">
-        <v>0.000248297968006512</v>
+        <v>0.0001950589075838755</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1785792681424108</v>
+        <v>0.1757441695002903</v>
       </c>
       <c r="I59" t="n">
-        <v>0.008023669565458087</v>
+        <v>0.005242485913674409</v>
       </c>
     </row>
     <row r="60">
@@ -2162,28 +2162,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.004844647508442402</v>
+        <v>0.005029300957500935</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0003381822844967246</v>
+        <v>0.0003882522275242955</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1815535782117844</v>
+        <v>0.1755100029449463</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003598697383284569</v>
+        <v>0.003763498734116554</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01137382202725523</v>
+        <v>0.008935262762666429</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0003122096263984337</v>
+        <v>0.0004821358053477065</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1915785557527526</v>
+        <v>0.176865318434079</v>
       </c>
       <c r="I60" t="n">
-        <v>0.01010371963428197</v>
+        <v>0.0075688003349083</v>
       </c>
     </row>
     <row r="61">
@@ -2191,28 +2191,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.004643509868264198</v>
+        <v>0.005789167741835117</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0003165494331428781</v>
+        <v>0.001788095121338964</v>
       </c>
       <c r="D61" t="n">
-        <v>0.1788943247842789</v>
+        <v>0.172756585896492</v>
       </c>
       <c r="E61" t="n">
-        <v>0.003432488863423467</v>
+        <v>0.003137289740025997</v>
       </c>
       <c r="F61" t="n">
-        <v>0.007060466996511082</v>
+        <v>0.09004782734745673</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0002740801411808497</v>
+        <v>0.08343668155238446</v>
       </c>
       <c r="H61" t="n">
-        <v>0.172359832235495</v>
+        <v>0.1907093448477507</v>
       </c>
       <c r="I61" t="n">
-        <v>0.005924587615569643</v>
+        <v>0.005657598804621721</v>
       </c>
     </row>
     <row r="62">
@@ -2220,28 +2220,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>0.00472444668841362</v>
+        <v>0.0068352919485569</v>
       </c>
       <c r="C62" t="n">
-        <v>0.000336611514961347</v>
+        <v>0.002984305179713294</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1780703453817367</v>
+        <v>0.1707801451787949</v>
       </c>
       <c r="E62" t="n">
-        <v>0.003497483456343412</v>
+        <v>0.002997086038917303</v>
       </c>
       <c r="F62" t="n">
-        <v>0.00694835787708909</v>
+        <v>0.009289885052460053</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0002220405503865529</v>
+        <v>0.0002966271396680791</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1728398401011845</v>
+        <v>0.1658252907538297</v>
       </c>
       <c r="I62" t="n">
-        <v>0.005862118132126808</v>
+        <v>0.008164131536526792</v>
       </c>
     </row>
     <row r="63">
@@ -2249,28 +2249,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.004531749555319548</v>
+        <v>0.004661692716538906</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0003476336145633832</v>
+        <v>0.0003295165308900177</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1788781044378281</v>
+        <v>0.1677743482685089</v>
       </c>
       <c r="E63" t="n">
-        <v>0.003289725418657065</v>
+        <v>0.003493304450064898</v>
       </c>
       <c r="F63" t="n">
-        <v>0.009715355528339282</v>
+        <v>0.005823409770194556</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0004184127015746875</v>
+        <v>0.0002409101164431446</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1787473555509651</v>
+        <v>0.1721460360006641</v>
       </c>
       <c r="I63" t="n">
-        <v>0.008403205934510875</v>
+        <v>0.004721769530350437</v>
       </c>
     </row>
     <row r="64">
@@ -2278,28 +2278,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.004476448991388083</v>
+        <v>0.004343966055065394</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0003179072421435267</v>
+        <v>0.0003747845054678619</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1778864272356033</v>
+        <v>0.168151059715271</v>
       </c>
       <c r="E64" t="n">
-        <v>0.003269109638944268</v>
+        <v>0.003128426241308451</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0084142298786787</v>
+        <v>0.007924130463556403</v>
       </c>
       <c r="G64" t="n">
-        <v>0.000308230822405673</v>
+        <v>0.000207382047376641</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1808572182637832</v>
+        <v>0.1721111115273605</v>
       </c>
       <c r="I64" t="n">
-        <v>0.00720171307312358</v>
+        <v>0.006856192795538494</v>
       </c>
     </row>
     <row r="65">
@@ -2307,28 +2307,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.004243875524282455</v>
+        <v>0.004405625957220793</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0003194029839104041</v>
+        <v>0.0003411122040841729</v>
       </c>
       <c r="D65" t="n">
-        <v>0.1728919500417709</v>
+        <v>0.1662684846372604</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00306001281195879</v>
+        <v>0.003233171292796731</v>
       </c>
       <c r="F65" t="n">
-        <v>0.008121869434795507</v>
+        <v>0.006033597302548648</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0002311579561000386</v>
+        <v>0.0002010564622906041</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1786147671578175</v>
+        <v>0.1678734749429183</v>
       </c>
       <c r="I65" t="n">
-        <v>0.006997637679985744</v>
+        <v>0.004993173505132486</v>
       </c>
     </row>
     <row r="66">
@@ -2336,28 +2336,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.004172048986777663</v>
+        <v>0.004204250801071525</v>
       </c>
       <c r="C66" t="n">
-        <v>0.000310194597762078</v>
+        <v>0.0003154977834932506</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1749940472955704</v>
+        <v>0.1654226778402328</v>
       </c>
       <c r="E66" t="n">
-        <v>0.002986884158536792</v>
+        <v>0.003061639656797051</v>
       </c>
       <c r="F66" t="n">
-        <v>0.006595646220200116</v>
+        <v>0.008144655278344527</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0002420619084033735</v>
+        <v>0.0003276245607170284</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1709859999338527</v>
+        <v>0.155790223289664</v>
       </c>
       <c r="I66" t="n">
-        <v>0.005498654307891747</v>
+        <v>0.00703807956175985</v>
       </c>
     </row>
     <row r="67">
@@ -2365,28 +2365,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.004105697636008263</v>
+        <v>0.004072880748540163</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0003222486817585305</v>
+        <v>0.0003175191258303821</v>
       </c>
       <c r="D67" t="n">
-        <v>0.1760195405139923</v>
+        <v>0.1632949312162399</v>
       </c>
       <c r="E67" t="n">
-        <v>0.002903351216897368</v>
+        <v>0.002938886995777488</v>
       </c>
       <c r="F67" t="n">
-        <v>0.00804060889581191</v>
+        <v>0.008509906753350723</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0002197951872935245</v>
+        <v>0.0002555378648960662</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1733017969967685</v>
+        <v>0.162366679342886</v>
       </c>
       <c r="I67" t="n">
-        <v>0.006954304694515603</v>
+        <v>0.007442535695545436</v>
       </c>
     </row>
     <row r="68">
@@ -2394,28 +2394,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.003897589916035533</v>
+        <v>0.004334587059095502</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0002811800561025739</v>
+        <v>0.0008860145611842162</v>
       </c>
       <c r="D68" t="n">
-        <v>0.1734378795137405</v>
+        <v>0.1633080668792725</v>
       </c>
       <c r="E68" t="n">
-        <v>0.002749220446825028</v>
+        <v>0.002632032160356641</v>
       </c>
       <c r="F68" t="n">
-        <v>0.006069644294332767</v>
+        <v>0.005352992635208135</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0002362935086869867</v>
+        <v>0.0001150265000882098</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1659232685451212</v>
+        <v>0.1688324673558915</v>
       </c>
       <c r="I68" t="n">
-        <v>0.005003734451413252</v>
+        <v>0.004393803888163112</v>
       </c>
     </row>
     <row r="69">
@@ -2423,28 +2423,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.003868361981481314</v>
+        <v>0.003685560397908092</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0003050773636884988</v>
+        <v>0.0003076580553734675</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1730113916215897</v>
+        <v>0.1613997250471115</v>
       </c>
       <c r="E69" t="n">
-        <v>0.002698227681718767</v>
+        <v>0.002570903723940253</v>
       </c>
       <c r="F69" t="n">
-        <v>0.007303161088249618</v>
+        <v>0.007752340039296066</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0003046115333777298</v>
+        <v>0.0004916380344947791</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1666487578087491</v>
+        <v>0.1613176002004602</v>
       </c>
       <c r="I69" t="n">
-        <v>0.006165305715036042</v>
+        <v>0.006454113934729947</v>
       </c>
     </row>
     <row r="70">
@@ -2452,28 +2452,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.00381622143727541</v>
+        <v>0.003826179561838507</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0003090749825388193</v>
+        <v>0.0003072854398936033</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1714768409070969</v>
+        <v>0.1585115858812332</v>
       </c>
       <c r="E70" t="n">
-        <v>0.002649762254297733</v>
+        <v>0.002726336244761944</v>
       </c>
       <c r="F70" t="n">
-        <v>0.008088971465023851</v>
+        <v>0.005376465290262201</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0002495955034340678</v>
+        <v>0.0001994001207251077</v>
       </c>
       <c r="H70" t="n">
-        <v>0.165385125739345</v>
+        <v>0.1638658841671407</v>
       </c>
       <c r="I70" t="n">
-        <v>0.007012450365291917</v>
+        <v>0.004357735724697349</v>
       </c>
     </row>
     <row r="71">
@@ -2481,28 +2481,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>0.004130742121458053</v>
+        <v>0.003608856943160296</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0008110789332389832</v>
+        <v>0.0002992543118828908</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1685364185781479</v>
+        <v>0.1588458614292145</v>
       </c>
       <c r="E71" t="n">
-        <v>0.002476981113284826</v>
+        <v>0.002515373343303799</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01166641810541246</v>
+        <v>0.00701684017023026</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00546658342461091</v>
+        <v>0.000272611925884744</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1763865682827901</v>
+        <v>0.1495366903444293</v>
       </c>
       <c r="I71" t="n">
-        <v>0.005317901748841778</v>
+        <v>0.005996544802740678</v>
       </c>
     </row>
     <row r="72">
@@ -2510,28 +2510,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0.003380328223019838</v>
+        <v>0.003546005917698145</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0004416235247673467</v>
+        <v>0.0003003088851217181</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1661330781888962</v>
+        <v>0.1568016759967804</v>
       </c>
       <c r="E72" t="n">
-        <v>0.002108039303302765</v>
+        <v>0.002461688675865531</v>
       </c>
       <c r="F72" t="n">
-        <v>0.00744288175277181</v>
+        <v>0.006323456488288392</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0003042579014697469</v>
+        <v>0.0001960969763199478</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1646451753805745</v>
+        <v>0.1533615525113039</v>
       </c>
       <c r="I72" t="n">
-        <v>0.00631539798391828</v>
+        <v>0.005360551730533652</v>
       </c>
     </row>
     <row r="73">
@@ -2539,28 +2539,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.003433634647518396</v>
+        <v>0.003469483434826136</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0002835748320836574</v>
+        <v>0.0003096993425954133</v>
       </c>
       <c r="D73" t="n">
-        <v>0.1670006456041336</v>
+        <v>0.1591236048116684</v>
       </c>
       <c r="E73" t="n">
-        <v>0.002315056608080864</v>
+        <v>0.002364166085615754</v>
       </c>
       <c r="F73" t="n">
-        <v>0.006023848573289824</v>
+        <v>0.006995568519449059</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0002130957425058839</v>
+        <v>0.000252719288124045</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1655054146819558</v>
+        <v>0.1537430555347906</v>
       </c>
       <c r="I73" t="n">
-        <v>0.00498322575947127</v>
+        <v>0.005974133922270276</v>
       </c>
     </row>
     <row r="74">
@@ -2568,28 +2568,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.003342567491695285</v>
+        <v>0.003378973057031632</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0003150589444041252</v>
+        <v>0.0002989625801257789</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1661289945240021</v>
+        <v>0.1574563458003998</v>
       </c>
       <c r="E74" t="n">
-        <v>0.002196863590821624</v>
+        <v>0.002292728795871138</v>
       </c>
       <c r="F74" t="n">
-        <v>0.03154715480559413</v>
+        <v>0.005629612321845372</v>
       </c>
       <c r="G74" t="n">
-        <v>0.02583933369880983</v>
+        <v>0.0001820921570937746</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1878988782684721</v>
+        <v>0.1551700589794903</v>
       </c>
       <c r="I74" t="n">
-        <v>0.004768327240077064</v>
+        <v>0.00467166986170591</v>
       </c>
     </row>
     <row r="75">
@@ -2597,28 +2597,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.004096910170868039</v>
+        <v>0.00330130180773139</v>
       </c>
       <c r="C75" t="n">
-        <v>0.00141497823369503</v>
+        <v>0.0002925815079445019</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1642954889278412</v>
+        <v>0.1559504538116455</v>
       </c>
       <c r="E75" t="n">
-        <v>0.001860454518318176</v>
+        <v>0.002228968057312071</v>
       </c>
       <c r="F75" t="n">
-        <v>0.006259294620625444</v>
+        <v>0.006522650523612589</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0002204337569206594</v>
+        <v>0.0003465817486400128</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1634457558743522</v>
+        <v>0.1514120882418961</v>
       </c>
       <c r="I75" t="n">
-        <v>0.005221632039159245</v>
+        <v>0.005419008376845577</v>
       </c>
     </row>
     <row r="76">
@@ -2626,28 +2626,28 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.003195025457829237</v>
+        <v>0.003203299562737346</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0002771940011847764</v>
+        <v>0.0002675670455452055</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1629536991930008</v>
+        <v>0.1531359881029129</v>
       </c>
       <c r="E76" t="n">
-        <v>0.002103062981598079</v>
+        <v>0.002170052604749799</v>
       </c>
       <c r="F76" t="n">
-        <v>0.005463237270749315</v>
+        <v>0.005998629999953226</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0001900711837275938</v>
+        <v>0.0002254490058551593</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1608206031528616</v>
+        <v>0.1535905394429678</v>
       </c>
       <c r="I76" t="n">
-        <v>0.004469063065879253</v>
+        <v>0.005005228353229763</v>
       </c>
     </row>
     <row r="77">
@@ -2655,28 +2655,28 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.003112796830266714</v>
+        <v>0.003186436864405871</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0002716665378231555</v>
+        <v>0.0002826611378295347</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1635046085586548</v>
+        <v>0.1541760752658844</v>
       </c>
       <c r="E77" t="n">
-        <v>0.002023607255324721</v>
+        <v>0.002132895398765803</v>
       </c>
       <c r="F77" t="n">
-        <v>0.006615565802391503</v>
+        <v>0.006297723742940298</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0003329516656459028</v>
+        <v>0.0002850664936201297</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1662385281371059</v>
+        <v>0.1529920014510536</v>
       </c>
       <c r="I77" t="n">
-        <v>0.005451421568635092</v>
+        <v>0.005247697279063854</v>
       </c>
     </row>
     <row r="78">
@@ -2684,28 +2684,28 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.002979803588986397</v>
+        <v>0.003098462510347367</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0002671214000908658</v>
+        <v>0.0002710751336924732</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1599123765964508</v>
+        <v>0.1537775944032669</v>
       </c>
       <c r="E78" t="n">
-        <v>0.001913120338961482</v>
+        <v>0.002058499412186444</v>
       </c>
       <c r="F78" t="n">
-        <v>0.006433149532978628</v>
+        <v>0.006317101086704076</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0001811718427776291</v>
+        <v>0.0002075320634116201</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1615051640635797</v>
+        <v>0.1597382941030172</v>
       </c>
       <c r="I78" t="n">
-        <v>0.005444451856288639</v>
+        <v>0.005310877532064671</v>
       </c>
     </row>
     <row r="79">
@@ -2713,28 +2713,28 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.002951711003750562</v>
+        <v>0.003038629263296724</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0002893721155505628</v>
+        <v>0.0002757268656259402</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1598795922346115</v>
+        <v>0.1535397916345596</v>
       </c>
       <c r="E79" t="n">
-        <v>0.001862940974496305</v>
+        <v>0.001995203434728086</v>
       </c>
       <c r="F79" t="n">
-        <v>0.006992858474433033</v>
+        <v>0.006463100407910678</v>
       </c>
       <c r="G79" t="n">
-        <v>0.000480442276622547</v>
+        <v>0.000261920487603513</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1651445196250524</v>
+        <v>0.1496556995967084</v>
       </c>
       <c r="I79" t="n">
-        <v>0.005686693584263859</v>
+        <v>0.005452901448683774</v>
       </c>
     </row>
     <row r="80">
@@ -2742,28 +2742,28 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.002931898242220283</v>
+        <v>0.003197248020410538</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0002719655749984086</v>
+        <v>0.000757366113406606</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1603387553920746</v>
+        <v>0.1545034746990204</v>
       </c>
       <c r="E80" t="n">
-        <v>0.001858238893181086</v>
+        <v>0.001667364532805979</v>
       </c>
       <c r="F80" t="n">
-        <v>0.005908346563140097</v>
+        <v>0.006452299980613817</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0002314054194659672</v>
+        <v>0.0001680410242718105</v>
       </c>
       <c r="H80" t="n">
-        <v>0.163491325539827</v>
+        <v>0.1522705164002361</v>
       </c>
       <c r="I80" t="n">
-        <v>0.004859484554090663</v>
+        <v>0.005522906415431865</v>
       </c>
     </row>
     <row r="81">
@@ -2771,28 +2771,28 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.002892688146576285</v>
+        <v>0.002817428652271628</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0002541544162910432</v>
+        <v>0.000264886839505285</v>
       </c>
       <c r="D81" t="n">
-        <v>0.1589035419530868</v>
+        <v>0.1506079057846069</v>
       </c>
       <c r="E81" t="n">
-        <v>0.001844016051709652</v>
+        <v>0.001799502301007509</v>
       </c>
       <c r="F81" t="n">
-        <v>0.006500114914740862</v>
+        <v>0.005939874752754343</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0003775122597320598</v>
+        <v>0.0002253145691462022</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1639788920610997</v>
+        <v>0.1592843479744567</v>
       </c>
       <c r="I81" t="n">
-        <v>0.005302708245765229</v>
+        <v>0.004918138528209283</v>
       </c>
     </row>
     <row r="82">
@@ -2800,28 +2800,28 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0.002736790425151586</v>
+        <v>0.002767774794027209</v>
       </c>
       <c r="C82" t="n">
-        <v>0.000244770908754319</v>
+        <v>0.0002659518567202612</v>
       </c>
       <c r="D82" t="n">
-        <v>0.158064817150116</v>
+        <v>0.150489259762764</v>
       </c>
       <c r="E82" t="n">
-        <v>0.001701695430912078</v>
+        <v>0.001749376659102738</v>
       </c>
       <c r="F82" t="n">
-        <v>0.006162044812954026</v>
+        <v>0.006678812565801583</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0002332973572749152</v>
+        <v>0.0002647768768298076</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1579929916495017</v>
+        <v>0.1467931095383101</v>
       </c>
       <c r="I82" t="n">
-        <v>0.005138782542107739</v>
+        <v>0.005680070190248345</v>
       </c>
     </row>
     <row r="83">
@@ -2829,28 +2829,28 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>0.002760052668660879</v>
+        <v>0.002668608663588762</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0002518097605276853</v>
+        <v>0.000249942525241524</v>
       </c>
       <c r="D83" t="n">
-        <v>0.1580212245960236</v>
+        <v>0.1486534023370743</v>
       </c>
       <c r="E83" t="n">
-        <v>0.001718136804938316</v>
+        <v>0.001675399159505963</v>
       </c>
       <c r="F83" t="n">
-        <v>0.006868841322792199</v>
+        <v>0.007258735114000555</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0004406504312489899</v>
+        <v>0.0002356228044438502</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1587406684543336</v>
+        <v>0.1537566965458638</v>
       </c>
       <c r="I83" t="n">
-        <v>0.005634487528341775</v>
+        <v>0.006254328850164499</v>
       </c>
     </row>
     <row r="84">
@@ -2858,28 +2858,28 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.00267896480025351</v>
+        <v>0.002716118378445506</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0002530952132251113</v>
+        <v>0.0002536625387482345</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1585216395750046</v>
+        <v>0.1477708577690124</v>
       </c>
       <c r="E84" t="n">
-        <v>0.001633261413902044</v>
+        <v>0.001723601557791233</v>
       </c>
       <c r="F84" t="n">
-        <v>0.006285936094297865</v>
+        <v>0.005792490105352822</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0002469992933724209</v>
+        <v>0.0001930633512829608</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1644434926229822</v>
+        <v>0.1443739344254987</v>
       </c>
       <c r="I84" t="n">
-        <v>0.005216719331538842</v>
+        <v>0.004877557112101532</v>
       </c>
     </row>
     <row r="85">
@@ -2887,28 +2887,28 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.002609606896013022</v>
+        <v>0.002743425396203995</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0002525024587567895</v>
+        <v>0.0003753870702385903</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1580300096359253</v>
+        <v>0.1482331673555374</v>
       </c>
       <c r="E85" t="n">
-        <v>0.001566954421758652</v>
+        <v>0.001626872504934669</v>
       </c>
       <c r="F85" t="n">
-        <v>0.005532081513582056</v>
+        <v>0.009704279567663471</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0002242978897181584</v>
+        <v>0.003986270192153691</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1605300841255639</v>
+        <v>0.1569235483089046</v>
       </c>
       <c r="I85" t="n">
-        <v>0.00450513320499469</v>
+        <v>0.004933391676617096</v>
       </c>
     </row>
     <row r="86">
@@ -2916,28 +2916,28 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.002566270223081112</v>
+        <v>0.002518923374801874</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0002448948816917837</v>
+        <v>0.0003398892346639186</v>
       </c>
       <c r="D86" t="n">
-        <v>0.156786994890213</v>
+        <v>0.1482211698360443</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00153744039927423</v>
+        <v>0.001437928271226585</v>
       </c>
       <c r="F86" t="n">
-        <v>0.006102396444543637</v>
+        <v>0.006390344241867981</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0002554162061426843</v>
+        <v>0.0003826245383323789</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1499899094820412</v>
+        <v>0.1504029412934675</v>
       </c>
       <c r="I86" t="n">
-        <v>0.005097030610891384</v>
+        <v>0.005255705110917133</v>
       </c>
     </row>
     <row r="87">
@@ -2945,28 +2945,28 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.002533134106084704</v>
+        <v>0.002452280125007033</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0002416358435899019</v>
+        <v>0.000251761783930473</v>
       </c>
       <c r="D87" t="n">
-        <v>0.1543945230436325</v>
+        <v>0.1461473505487442</v>
       </c>
       <c r="E87" t="n">
-        <v>0.001519525660976768</v>
+        <v>0.001469781618215144</v>
       </c>
       <c r="F87" t="n">
-        <v>0.005420656845240958</v>
+        <v>0.00495339620530265</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0001827439583857357</v>
+        <v>0.0001769584898586608</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1505505148913304</v>
+        <v>0.1450641046641896</v>
       </c>
       <c r="I87" t="n">
-        <v>0.004485160315418418</v>
+        <v>0.004051117200045854</v>
       </c>
     </row>
     <row r="88">
@@ -2974,28 +2974,28 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002416151955738664</v>
+        <v>0.002408146193817258</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0002468140153018757</v>
+        <v>0.0002451771073611453</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1539784128189087</v>
+        <v>0.1458081832008362</v>
       </c>
       <c r="E88" t="n">
-        <v>0.001399445882629603</v>
+        <v>0.001433928204506636</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006083776212128739</v>
+        <v>0.006048773369960013</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0002502099161080372</v>
+        <v>0.0003133192696501493</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1527128499969962</v>
+        <v>0.1403069938532097</v>
       </c>
       <c r="I88" t="n">
-        <v>0.005070002046011109</v>
+        <v>0.005033919134254751</v>
       </c>
     </row>
     <row r="89">
@@ -3003,28 +3003,28 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.002420810843914747</v>
+        <v>0.002345098574072123</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0002441519772149622</v>
+        <v>0.0002536899280585348</v>
       </c>
       <c r="D89" t="n">
-        <v>0.154255093914032</v>
+        <v>0.1463253999204636</v>
       </c>
       <c r="E89" t="n">
-        <v>0.001405383443042636</v>
+        <v>0.001359781665250659</v>
       </c>
       <c r="F89" t="n">
-        <v>0.005480540899915369</v>
+        <v>0.006375813057545882</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0001534681595659847</v>
+        <v>0.0002273804961191338</v>
       </c>
       <c r="H89" t="n">
-        <v>0.154870230129648</v>
+        <v>0.1417554389234468</v>
       </c>
       <c r="I89" t="n">
-        <v>0.004552721607591501</v>
+        <v>0.00543965539905633</v>
       </c>
     </row>
     <row r="90">
@@ -3032,28 +3032,28 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.00232406684101373</v>
+        <v>0.002374369464695453</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0002428725664764643</v>
+        <v>0.0002323328138049692</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1525010583305359</v>
+        <v>0.1447516410961151</v>
       </c>
       <c r="E90" t="n">
-        <v>0.001318688997887075</v>
+        <v>0.001418278467014432</v>
       </c>
       <c r="F90" t="n">
-        <v>0.005804338894334742</v>
+        <v>0.006204665987243417</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0002914053343405847</v>
+        <v>0.0002157036112021308</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1507876311274182</v>
+        <v>0.1425031725014598</v>
       </c>
       <c r="I90" t="n">
-        <v>0.004758995396676086</v>
+        <v>0.005276446580206201</v>
       </c>
     </row>
     <row r="91">
@@ -3061,28 +3061,28 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.002261513725727797</v>
+        <v>0.002256771184131503</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0002359068954754621</v>
+        <v>0.0002619125829534605</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1515039966497421</v>
+        <v>0.1457067557935715</v>
       </c>
       <c r="E91" t="n">
-        <v>0.0012680868774876</v>
+        <v>0.001266324859142303</v>
       </c>
       <c r="F91" t="n">
-        <v>0.00591224288771485</v>
+        <v>0.006423166311736451</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0001696384587396562</v>
+        <v>0.0002446176514707864</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1528153412017309</v>
+        <v>0.1412056274145696</v>
       </c>
       <c r="I91" t="n">
-        <v>0.004978527775335127</v>
+        <v>0.005472520487276658</v>
       </c>
     </row>
     <row r="92">
@@ -3090,28 +3090,28 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>0.002224753852382302</v>
+        <v>0.002232679542824626</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0002281967544928193</v>
+        <v>0.0002423309866711497</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1504413354063034</v>
+        <v>0.1439321658115387</v>
       </c>
       <c r="E92" t="n">
-        <v>0.001244350429050624</v>
+        <v>0.001270687723562121</v>
       </c>
       <c r="F92" t="n">
-        <v>0.006329722497460309</v>
+        <v>0.005507180289096437</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0003090789866539517</v>
+        <v>0.0001950363423215714</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1494614955836369</v>
+        <v>0.1472291455854211</v>
       </c>
       <c r="I92" t="n">
-        <v>0.005273336097750004</v>
+        <v>0.004575998268134248</v>
       </c>
     </row>
     <row r="93">
@@ -3119,28 +3119,28 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.002207986389838159</v>
+        <v>0.002164131432473659</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0002388720768941566</v>
+        <v>0.000239994201079011</v>
       </c>
       <c r="D93" t="n">
-        <v>0.1502382684469223</v>
+        <v>0.143007439450264</v>
       </c>
       <c r="E93" t="n">
-        <v>0.001217922985136509</v>
+        <v>0.001209100066199899</v>
       </c>
       <c r="F93" t="n">
-        <v>0.005801963501413874</v>
+        <v>0.005356249978969429</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0002622050242528903</v>
+        <v>0.0001967292144519716</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1522544102499575</v>
+        <v>0.143339507533131</v>
       </c>
       <c r="I93" t="n">
-        <v>0.004778486434537401</v>
+        <v>0.004442823306911095</v>
       </c>
     </row>
     <row r="94">
@@ -3148,28 +3148,28 @@
         <v>92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.002144897252559662</v>
+        <v>0.002133333856254816</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0002315718028889969</v>
+        <v>0.0002292185366237536</v>
       </c>
       <c r="D94" t="n">
-        <v>0.1503663008356094</v>
+        <v>0.1412461296224594</v>
       </c>
       <c r="E94" t="n">
-        <v>0.001161493967972696</v>
+        <v>0.001197884702399373</v>
       </c>
       <c r="F94" t="n">
-        <v>0.005941848371475692</v>
+        <v>0.006180474395798383</v>
       </c>
       <c r="G94" t="n">
-        <v>0.0002116525696353534</v>
+        <v>0.0003408437745826438</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1446456538162652</v>
+        <v>0.1382167771638509</v>
       </c>
       <c r="I94" t="n">
-        <v>0.005006967575075089</v>
+        <v>0.005148546758334214</v>
       </c>
     </row>
     <row r="95">
@@ -3177,28 +3177,28 @@
         <v>93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.00212193468914926</v>
+        <v>0.002064833130151033</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0002288783108945936</v>
+        <v>0.0002413878591274843</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1498018414773941</v>
+        <v>0.140564627289772</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00114404718054831</v>
+        <v>0.001120622133940458</v>
       </c>
       <c r="F95" t="n">
-        <v>0.005950696917120094</v>
+        <v>0.005028181764742339</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0002200456812133067</v>
+        <v>0.0002116338685033372</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1480370932486862</v>
+        <v>0.1415689049226036</v>
       </c>
       <c r="I95" t="n">
-        <v>0.004990465824429985</v>
+        <v>0.00410870342298151</v>
       </c>
     </row>
     <row r="96">
@@ -3206,28 +3206,28 @@
         <v>94</v>
       </c>
       <c r="B96" t="n">
-        <v>0.002047496133342385</v>
+        <v>0.002066438501857221</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0002300211954284459</v>
+        <v>0.0002349939589779824</v>
       </c>
       <c r="D96" t="n">
-        <v>0.14740084790802</v>
+        <v>0.1406122721366882</v>
       </c>
       <c r="E96" t="n">
-        <v>0.001080470712505281</v>
+        <v>0.001128383177369833</v>
       </c>
       <c r="F96" t="n">
-        <v>0.005247630353828628</v>
+        <v>0.006251944316608822</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0001806120077430287</v>
+        <v>0.0002410428484557668</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1469473511233415</v>
+        <v>0.1398505728095041</v>
       </c>
       <c r="I96" t="n">
-        <v>0.004332281593719518</v>
+        <v>0.005311648594139548</v>
       </c>
     </row>
     <row r="97">
@@ -3235,28 +3235,28 @@
         <v>95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.002017696129783988</v>
+        <v>0.001994269194826484</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0002247806956060231</v>
+        <v>0.0002353859281092882</v>
       </c>
       <c r="D97" t="n">
-        <v>0.1461149452972412</v>
+        <v>0.1404466670722961</v>
       </c>
       <c r="E97" t="n">
-        <v>0.001062340736992657</v>
+        <v>0.001056649949964136</v>
       </c>
       <c r="F97" t="n">
-        <v>0.00551548566453487</v>
+        <v>0.004943970901888551</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0001764590758080161</v>
+        <v>0.000180697623107789</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1522112145723371</v>
+        <v>0.1432685724634914</v>
       </c>
       <c r="I97" t="n">
-        <v>0.004577970545173761</v>
+        <v>0.004046930446066145</v>
       </c>
     </row>
     <row r="98">
@@ -3264,28 +3264,28 @@
         <v>96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.001970100699022412</v>
+        <v>0.00197703085488081</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0002266005973704159</v>
+        <v>0.0002303135488638654</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1471841026105881</v>
+        <v>0.1408385581064224</v>
       </c>
       <c r="E98" t="n">
-        <v>0.001007579601634294</v>
+        <v>0.001042524520397186</v>
       </c>
       <c r="F98" t="n">
-        <v>0.005466302742036045</v>
+        <v>0.00600416308594032</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0001800352305929339</v>
+        <v>0.0002262673877026934</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1498448765948779</v>
+        <v>0.1407424405844332</v>
       </c>
       <c r="I98" t="n">
-        <v>0.004537043120791045</v>
+        <v>0.005074183548546926</v>
       </c>
     </row>
     <row r="99">
@@ -3293,28 +3293,28 @@
         <v>97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.001950880081385374</v>
+        <v>0.001903775930166245</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0002219327430892736</v>
+        <v>0.0002240526552461088</v>
       </c>
       <c r="D99" t="n">
-        <v>0.1465974905023575</v>
+        <v>0.1384564649839401</v>
       </c>
       <c r="E99" t="n">
-        <v>0.0009959598903991282</v>
+        <v>0.0009874409350492061</v>
       </c>
       <c r="F99" t="n">
-        <v>0.006106927513280127</v>
+        <v>0.005636491641937033</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0002826433568804709</v>
+        <v>0.0001995628513528724</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1416873918155278</v>
+        <v>0.1376620539560987</v>
       </c>
       <c r="I99" t="n">
-        <v>0.005115847172273313</v>
+        <v>0.004748618511899358</v>
       </c>
     </row>
     <row r="100">
@@ -3322,28 +3322,28 @@
         <v>98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.001926317681074142</v>
+        <v>0.001899914828911424</v>
       </c>
       <c r="C100" t="n">
-        <v>0.000228327793193981</v>
+        <v>0.0002322251983610913</v>
       </c>
       <c r="D100" t="n">
-        <v>0.1463984179487229</v>
+        <v>0.1393649876585007</v>
       </c>
       <c r="E100" t="n">
-        <v>0.000965997821599245</v>
+        <v>0.0009708647080026567</v>
       </c>
       <c r="F100" t="n">
-        <v>0.006059658467423226</v>
+        <v>0.00576832145163835</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0001910805183021826</v>
+        <v>0.0002333877862157258</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1432413021240499</v>
+        <v>0.1386459573077533</v>
       </c>
       <c r="I100" t="n">
-        <v>0.005152371476691514</v>
+        <v>0.004841703907518266</v>
       </c>
     </row>
     <row r="101">
@@ -3351,28 +3351,28 @@
         <v>99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.001854881379008293</v>
+        <v>0.001830295632690191</v>
       </c>
       <c r="C101" t="n">
-        <v>0.000222781723709777</v>
+        <v>0.0002169401582125574</v>
       </c>
       <c r="D101" t="n">
-        <v>0.1451872455682754</v>
+        <v>0.1383284427137375</v>
       </c>
       <c r="E101" t="n">
-        <v>0.0009061634471751749</v>
+        <v>0.0009217132782153785</v>
       </c>
       <c r="F101" t="n">
-        <v>0.005481765722342407</v>
+        <v>0.005455407733477494</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0002482772436550155</v>
+        <v>0.0002119048017403415</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1466177156319626</v>
+        <v>0.1365510521880176</v>
       </c>
       <c r="I101" t="n">
-        <v>0.004500399880250991</v>
+        <v>0.004560747671428745</v>
       </c>
     </row>
     <row r="102">
@@ -3380,28 +3380,28 @@
         <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>0.001868652929976582</v>
+        <v>0.001837786268189549</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0002230283882692456</v>
+        <v>0.0002278741394411773</v>
       </c>
       <c r="D102" t="n">
-        <v>0.1448097451496124</v>
+        <v>0.1371822666063309</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0009215758364498615</v>
+        <v>0.0009240008087754249</v>
       </c>
       <c r="F102" t="n">
-        <v>0.005384487984899498</v>
+        <v>0.004967060071913006</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0002289819069222667</v>
+        <v>0.0001977335204657845</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1443185921010924</v>
+        <v>0.1382499047399151</v>
       </c>
       <c r="I102" t="n">
-        <v>0.004433913127979534</v>
+        <v>0.004078077051825032</v>
       </c>
     </row>
     <row r="103">
@@ -3409,28 +3409,28 @@
         <v>101</v>
       </c>
       <c r="B103" t="n">
-        <v>0.001814377841584384</v>
+        <v>0.001781635829657316</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0002187237746082246</v>
+        <v>0.000221386354486458</v>
       </c>
       <c r="D103" t="n">
-        <v>0.1448480884857178</v>
+        <v>0.1367291212005615</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0008714136295840144</v>
+        <v>0.0008766038862392307</v>
       </c>
       <c r="F103" t="n">
-        <v>0.00566963880956416</v>
+        <v>0.006086857517388137</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0002604683571560445</v>
+        <v>0.0002622195559843986</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1413788348961421</v>
+        <v>0.1381921904248476</v>
       </c>
       <c r="I103" t="n">
-        <v>0.004702276285269813</v>
+        <v>0.005133677046794633</v>
       </c>
     </row>
     <row r="104">
@@ -3438,28 +3438,28 @@
         <v>102</v>
       </c>
       <c r="B104" t="n">
-        <v>0.001805067232199013</v>
+        <v>0.001785843734294176</v>
       </c>
       <c r="C104" t="n">
-        <v>0.000218433141477406</v>
+        <v>0.000220768480475992</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1437682714385986</v>
+        <v>0.1357377985630036</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0008677927380055189</v>
+        <v>0.0008863862734120339</v>
       </c>
       <c r="F104" t="n">
-        <v>0.005646961505447331</v>
+        <v>0.005215661324633568</v>
       </c>
       <c r="G104" t="n">
-        <v>0.000216349937192842</v>
+        <v>0.0001956059692378519</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1449942178273084</v>
+        <v>0.1361107449304027</v>
       </c>
       <c r="I104" t="n">
-        <v>0.004705640512471487</v>
+        <v>0.004339501665066471</v>
       </c>
     </row>
     <row r="105">
@@ -3467,28 +3467,28 @@
         <v>103</v>
       </c>
       <c r="B105" t="n">
-        <v>0.001752084528297186</v>
+        <v>0.00167810264505446</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0002158964675953612</v>
+        <v>0.0002191560261193663</v>
       </c>
       <c r="D105" t="n">
-        <v>0.1432251273517609</v>
+        <v>0.1368235355854034</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0008200624230206013</v>
+        <v>0.0007748289787545801</v>
       </c>
       <c r="F105" t="n">
-        <v>0.005339126375885179</v>
+        <v>0.005045836252839491</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0001828694245838796</v>
+        <v>0.000219453555782672</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1439818530623325</v>
+        <v>0.1365274081883578</v>
       </c>
       <c r="I105" t="n">
-        <v>0.004436347712542357</v>
+        <v>0.004143745590086425</v>
       </c>
     </row>
     <row r="106">
@@ -3496,28 +3496,28 @@
         <v>104</v>
       </c>
       <c r="B106" t="n">
-        <v>0.001705937257900834</v>
+        <v>0.001703882086053491</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0002145796970529482</v>
+        <v>0.0002246426113694906</v>
       </c>
       <c r="D106" t="n">
-        <v>0.1422015170793533</v>
+        <v>0.1363809589805603</v>
       </c>
       <c r="E106" t="n">
-        <v>0.0007803499981537461</v>
+        <v>0.0007973346961215139</v>
       </c>
       <c r="F106" t="n">
-        <v>0.005443288112031888</v>
+        <v>0.005770181611933872</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0002592688482342102</v>
+        <v>0.0002174730667275442</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1457748759220708</v>
+        <v>0.135448352749935</v>
       </c>
       <c r="I106" t="n">
-        <v>0.004455144910466953</v>
+        <v>0.004875466761135209</v>
       </c>
     </row>
     <row r="107">
@@ -3525,28 +3525,28 @@
         <v>105</v>
       </c>
       <c r="B107" t="n">
-        <v>0.001685824241951108</v>
+        <v>0.001667578193590045</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0002095437746075913</v>
+        <v>0.0002142245633229613</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1420856988897324</v>
+        <v>0.1343795343141556</v>
       </c>
       <c r="E107" t="n">
-        <v>0.000765851992290467</v>
+        <v>0.0007814559866152704</v>
       </c>
       <c r="F107" t="n">
-        <v>0.005019707829398247</v>
+        <v>0.004777364635849174</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0001991829915476589</v>
+        <v>0.0001739957752686182</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1402800355815187</v>
+        <v>0.1348928031301032</v>
       </c>
       <c r="I107" t="n">
-        <v>0.00411912468793767</v>
+        <v>0.003928904884295815</v>
       </c>
     </row>
     <row r="108">
@@ -3554,28 +3554,28 @@
         <v>106</v>
       </c>
       <c r="B108" t="n">
-        <v>0.001672935761556029</v>
+        <v>0.001633679234534502</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0002121083833873272</v>
+        <v>0.0002185436797188595</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1420394370718002</v>
+        <v>0.134525151143074</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0007506302037611604</v>
+        <v>0.0007425098190754653</v>
       </c>
       <c r="F108" t="n">
-        <v>0.005609987905890138</v>
+        <v>0.005841969471838064</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0002287238605784216</v>
+        <v>0.0002284714136919125</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1389261113002677</v>
+        <v>0.131962135013126</v>
       </c>
       <c r="I108" t="n">
-        <v>0.004686633449998878</v>
+        <v>0.004953687469950508</v>
       </c>
     </row>
     <row r="109">
@@ -3583,28 +3583,28 @@
         <v>107</v>
       </c>
       <c r="B109" t="n">
-        <v>0.001606878625065088</v>
+        <v>0.001603480898380279</v>
       </c>
       <c r="C109" t="n">
-        <v>0.000212781053205952</v>
+        <v>0.0002105851868074387</v>
       </c>
       <c r="D109" t="n">
-        <v>0.1404341247987747</v>
+        <v>0.1342933037242889</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0006919269559048116</v>
+        <v>0.0007214292153082788</v>
       </c>
       <c r="F109" t="n">
-        <v>0.00555022930562326</v>
+        <v>0.004954550866566319</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0001867183419367979</v>
+        <v>0.00017666636046146</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1407497927794449</v>
+        <v>0.1335101947047388</v>
       </c>
       <c r="I109" t="n">
-        <v>0.004659761981051081</v>
+        <v>0.004110333529433166</v>
       </c>
     </row>
     <row r="110">
@@ -3612,28 +3612,28 @@
         <v>108</v>
       </c>
       <c r="B110" t="n">
-        <v>0.001594049569115043</v>
+        <v>0.001586449990510941</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0002111334532871842</v>
+        <v>0.0002208307294398546</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1400008265810013</v>
+        <v>0.1340164628219604</v>
       </c>
       <c r="E110" t="n">
-        <v>0.0006829119967855513</v>
+        <v>0.0006955369613915682</v>
       </c>
       <c r="F110" t="n">
-        <v>0.005344920873727048</v>
+        <v>0.005522044763868435</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0001780712824686298</v>
+        <v>0.0002619893249233677</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1430951407731649</v>
+        <v>0.1348454090704926</v>
       </c>
       <c r="I110" t="n">
-        <v>0.004451373910431129</v>
+        <v>0.004585828397021937</v>
       </c>
     </row>
     <row r="111">
@@ -3641,28 +3641,28 @@
         <v>109</v>
       </c>
       <c r="B111" t="n">
-        <v>0.001558179196879268</v>
+        <v>0.001533062110476196</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0002099166595153511</v>
+        <v>0.0002129485925240442</v>
       </c>
       <c r="D111" t="n">
-        <v>0.1403000102119446</v>
+        <v>0.1332730743150711</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0006467624920718372</v>
+        <v>0.0006537481610886753</v>
       </c>
       <c r="F111" t="n">
-        <v>0.005541590101451751</v>
+        <v>0.004885170867098389</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0002199792487823691</v>
+        <v>0.0001978792162873398</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1387032560267612</v>
+        <v>0.1324155069243461</v>
       </c>
       <c r="I111" t="n">
-        <v>0.004628094598669164</v>
+        <v>0.004025214106987001</v>
       </c>
     </row>
     <row r="112">
@@ -3670,28 +3670,28 @@
         <v>110</v>
       </c>
       <c r="B112" t="n">
-        <v>0.001541075913205743</v>
+        <v>0.001519319551259279</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0002074863482490182</v>
+        <v>0.0002085499865077436</v>
       </c>
       <c r="D112" t="n">
-        <v>0.1397498220911026</v>
+        <v>0.1325183969392776</v>
       </c>
       <c r="E112" t="n">
-        <v>0.0006348404718451202</v>
+        <v>0.0006481775922253728</v>
       </c>
       <c r="F112" t="n">
-        <v>0.005565835512554665</v>
+        <v>0.005545285608418906</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0002159539977615383</v>
+        <v>0.0002292040878248615</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1412472228883336</v>
+        <v>0.1310234190949024</v>
       </c>
       <c r="I112" t="n">
-        <v>0.004643645381393917</v>
+        <v>0.004660964429220504</v>
       </c>
     </row>
     <row r="113">
@@ -3699,28 +3699,28 @@
         <v>111</v>
       </c>
       <c r="B113" t="n">
-        <v>0.001525364038020372</v>
+        <v>0.001478935258939862</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0002066048928918317</v>
+        <v>0.0002100140989646316</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1397114882268906</v>
+        <v>0.1325164592275619</v>
       </c>
       <c r="E113" t="n">
-        <v>0.0006202017334662377</v>
+        <v>0.0006063388730064035</v>
       </c>
       <c r="F113" t="n">
-        <v>0.005044321037683071</v>
+        <v>0.005685659706483171</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0002000818870730735</v>
+        <v>0.0002350648135304995</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1373375772029696</v>
+        <v>0.1335506354440095</v>
       </c>
       <c r="I113" t="n">
-        <v>0.004157551330564389</v>
+        <v>0.004782841713372831</v>
       </c>
     </row>
     <row r="114">
@@ -3728,28 +3728,28 @@
         <v>112</v>
       </c>
       <c r="B114" t="n">
-        <v>0.00151376187235862</v>
+        <v>0.001489660162776709</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0002062965891752392</v>
+        <v>0.0002067387491995469</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1397424994277954</v>
+        <v>0.1322951504068375</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0006087528150007129</v>
+        <v>0.0006214456826485694</v>
       </c>
       <c r="F114" t="n">
-        <v>0.005410260602552292</v>
+        <v>0.005463995743591527</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0002313251153261706</v>
+        <v>0.0002169557579070995</v>
       </c>
       <c r="H114" t="n">
-        <v>0.135884792702622</v>
+        <v>0.133677965838213</v>
       </c>
       <c r="I114" t="n">
-        <v>0.004499511542239304</v>
+        <v>0.004578650152252996</v>
       </c>
     </row>
     <row r="115">
@@ -3757,28 +3757,28 @@
         <v>113</v>
       </c>
       <c r="B115" t="n">
-        <v>0.001467974789701402</v>
+        <v>0.001463139889337122</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0002058555576018989</v>
+        <v>0.0002073076739041135</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1382985404682159</v>
+        <v>0.1318046484203339</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0005706265413574875</v>
+        <v>0.0005968089775517583</v>
       </c>
       <c r="F115" t="n">
-        <v>0.005568389640832365</v>
+        <v>0.005709633384884425</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0001969155822688756</v>
+        <v>0.0002479413145891775</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1376025418706275</v>
+        <v>0.1306323103492451</v>
       </c>
       <c r="I115" t="n">
-        <v>0.004683461404795991</v>
+        <v>0.004808530464349087</v>
       </c>
     </row>
     <row r="116">
@@ -3786,28 +3786,28 @@
         <v>114</v>
       </c>
       <c r="B116" t="n">
-        <v>0.001448221477024257</v>
+        <v>0.001438991415023804</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0002054873071471229</v>
+        <v>0.0002140433181682602</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1381269327497482</v>
+        <v>0.132167779253006</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0005520995228216053</v>
+        <v>0.0005641092015951872</v>
       </c>
       <c r="F116" t="n">
-        <v>0.005166047893640803</v>
+        <v>0.004724342212822368</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0002290862658811994</v>
+        <v>0.000235144157084366</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1336262830717529</v>
+        <v>0.1292477891670744</v>
       </c>
       <c r="I116" t="n">
-        <v>0.004268830221474511</v>
+        <v>0.003842959182358197</v>
       </c>
     </row>
     <row r="117">
@@ -3815,28 +3815,28 @@
         <v>115</v>
       </c>
       <c r="B117" t="n">
-        <v>0.001442341488368809</v>
+        <v>0.001413907471962273</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0002018581819022074</v>
+        <v>0.0002017106101047248</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1371428882703781</v>
+        <v>0.131271568444252</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0005547688815779984</v>
+        <v>0.0005558390378803015</v>
       </c>
       <c r="F117" t="n">
-        <v>0.004917969249194977</v>
+        <v>0.004745430515313348</v>
       </c>
       <c r="G117" t="n">
-        <v>0.0001949888806826956</v>
+        <v>0.0001822697570755224</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1385521077195739</v>
+        <v>0.1347587533545533</v>
       </c>
       <c r="I117" t="n">
-        <v>0.004030219835744256</v>
+        <v>0.003889367005652573</v>
       </c>
     </row>
     <row r="118">
@@ -3844,28 +3844,28 @@
         <v>116</v>
       </c>
       <c r="B118" t="n">
-        <v>0.001416172398045659</v>
+        <v>0.001379607236012816</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0002043029767163098</v>
+        <v>0.0002046671372540295</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1370494688901901</v>
+        <v>0.1313253065834045</v>
       </c>
       <c r="E118" t="n">
-        <v>0.0005266220888532698</v>
+        <v>0.0005183135936148465</v>
       </c>
       <c r="F118" t="n">
-        <v>0.005257096192715948</v>
+        <v>0.005449401681747464</v>
       </c>
       <c r="G118" t="n">
-        <v>0.0002338680023181998</v>
+        <v>0.0002549957634017424</v>
       </c>
       <c r="H118" t="n">
-        <v>0.135605714016793</v>
+        <v>0.1316601363014047</v>
       </c>
       <c r="I118" t="n">
-        <v>0.004345199609658458</v>
+        <v>0.00453610530973915</v>
       </c>
     </row>
     <row r="119">
@@ -3873,28 +3873,28 @@
         <v>117</v>
       </c>
       <c r="B119" t="n">
-        <v>0.001404937186285853</v>
+        <v>0.001352539452508092</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0002034697165479884</v>
+        <v>0.0002043149307817221</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1369633253107071</v>
+        <v>0.1308256526241303</v>
       </c>
       <c r="E119" t="n">
-        <v>0.0005166508560795337</v>
+        <v>0.0004940962765291333</v>
       </c>
       <c r="F119" t="n">
-        <v>0.004819441599039085</v>
+        <v>0.005041174238963967</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0001949443179790423</v>
+        <v>0.0001855825750583777</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1374706851152573</v>
+        <v>0.1320194230188553</v>
       </c>
       <c r="I119" t="n">
-        <v>0.003937143880864803</v>
+        <v>0.004195494501081221</v>
       </c>
     </row>
     <row r="120">
@@ -3902,28 +3902,28 @@
         <v>118</v>
       </c>
       <c r="B120" t="n">
-        <v>0.001382543397456408</v>
+        <v>0.001330198597460985</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0002024137360770255</v>
+        <v>0.0002024055759105831</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1362865125255585</v>
+        <v>0.1301336919631958</v>
       </c>
       <c r="E120" t="n">
-        <v>0.0004986971128769219</v>
+        <v>0.0004771245766617358</v>
       </c>
       <c r="F120" t="n">
-        <v>0.005359160680335993</v>
+        <v>0.004982084427636609</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0002586651667815802</v>
+        <v>0.0002130717945201201</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1354772709399996</v>
+        <v>0.1298537775509509</v>
       </c>
       <c r="I120" t="n">
-        <v>0.004423109157706746</v>
+        <v>0.004119743761374064</v>
       </c>
     </row>
     <row r="121">
@@ -3931,28 +3931,28 @@
         <v>119</v>
       </c>
       <c r="B121" t="n">
-        <v>0.001344778327248991</v>
+        <v>0.001336318010672927</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0002018820155281574</v>
+        <v>0.0002021216835584491</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1360318210506439</v>
+        <v>0.1310653746013641</v>
       </c>
       <c r="E121" t="n">
-        <v>0.0004627372174188495</v>
+        <v>0.0004788694660924375</v>
       </c>
       <c r="F121" t="n">
-        <v>0.00489347634018136</v>
+        <v>0.005462170745752034</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0002039178276850825</v>
+        <v>0.0002395419047153699</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1369840321085776</v>
+        <v>0.1297063948396368</v>
       </c>
       <c r="I121" t="n">
-        <v>0.004004638312873696</v>
+        <v>0.004574096929312336</v>
       </c>
     </row>
     <row r="122">
@@ -3960,28 +3960,28 @@
         <v>120</v>
       </c>
       <c r="B122" t="n">
-        <v>0.001353173660591245</v>
+        <v>0.001328412542194128</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0001990876456107944</v>
+        <v>0.0001986007265113294</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1361039838323593</v>
+        <v>0.1304590854511261</v>
       </c>
       <c r="E122" t="n">
-        <v>0.0004735661012325436</v>
+        <v>0.0004775163954719901</v>
       </c>
       <c r="F122" t="n">
-        <v>0.005135241600473641</v>
+        <v>0.00487981743244591</v>
       </c>
       <c r="G122" t="n">
-        <v>0.0002247500305527785</v>
+        <v>0.0001962509985176047</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1362307569836715</v>
+        <v>0.129307362221388</v>
       </c>
       <c r="I122" t="n">
-        <v>0.004229337837240168</v>
+        <v>0.004037029629354449</v>
       </c>
     </row>
     <row r="123">
@@ -3989,28 +3989,28 @@
         <v>121</v>
       </c>
       <c r="B123" t="n">
-        <v>0.001320267982795834</v>
+        <v>0.001301373737677932</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0001982450561402366</v>
+        <v>0.0001996730601340532</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1360176824588776</v>
+        <v>0.1299631513490677</v>
       </c>
       <c r="E123" t="n">
-        <v>0.0004419345382768661</v>
+        <v>0.0004518849398717284</v>
       </c>
       <c r="F123" t="n">
-        <v>0.004773130024803064</v>
+        <v>0.005254859498095794</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0001805431986106848</v>
+        <v>0.000210514394342322</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1362926047612559</v>
+        <v>0.1283817787495173</v>
       </c>
       <c r="I123" t="n">
-        <v>0.003911123814845236</v>
+        <v>0.004402436229505167</v>
       </c>
     </row>
     <row r="124">
@@ -4018,28 +4018,28 @@
         <v>122</v>
       </c>
       <c r="B124" t="n">
-        <v>0.001307333604633808</v>
+        <v>0.001273544439867139</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0001992898224648088</v>
+        <v>0.0001997213439494371</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1357360863075256</v>
+        <v>0.1299341140470505</v>
       </c>
       <c r="E124" t="n">
-        <v>0.0004293633526116609</v>
+        <v>0.0004241525427512825</v>
       </c>
       <c r="F124" t="n">
-        <v>0.005236025049820616</v>
+        <v>0.004880912453908516</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0002128860058732404</v>
+        <v>0.0001849969947753553</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1359093516014918</v>
+        <v>0.1288240459080038</v>
       </c>
       <c r="I124" t="n">
-        <v>0.004343592257194866</v>
+        <v>0.004051795270974591</v>
       </c>
     </row>
     <row r="125">
@@ -4047,28 +4047,28 @@
         <v>123</v>
       </c>
       <c r="B125" t="n">
-        <v>0.001290539313726127</v>
+        <v>0.001276695708081126</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0001976209669765085</v>
+        <v>0.0001976964520961046</v>
       </c>
       <c r="D125" t="n">
-        <v>0.135530974322319</v>
+        <v>0.1294282086057663</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0004152634771838784</v>
+        <v>0.0004318582241386175</v>
       </c>
       <c r="F125" t="n">
-        <v>0.004889638279952097</v>
+        <v>0.005196468045670679</v>
       </c>
       <c r="G125" t="n">
-        <v>0.0001811180056479561</v>
+        <v>0.0001947642506277234</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1361385690533901</v>
+        <v>0.129144518104113</v>
       </c>
       <c r="I125" t="n">
-        <v>0.004027827445836966</v>
+        <v>0.004355981205065916</v>
       </c>
     </row>
     <row r="126">
@@ -4076,28 +4076,28 @@
         <v>124</v>
       </c>
       <c r="B126" t="n">
-        <v>0.001263001810975373</v>
+        <v>0.001244696606457233</v>
       </c>
       <c r="C126" t="n">
-        <v>0.000196633097326383</v>
+        <v>0.0001965818446604535</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1355027211341858</v>
+        <v>0.1295005146560669</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0003888551122117788</v>
+        <v>0.0004006122000589967</v>
       </c>
       <c r="F126" t="n">
-        <v>0.005015411962486111</v>
+        <v>0.004815012073998155</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0002128667194000483</v>
+        <v>0.0001871900546919406</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1358465641464728</v>
+        <v>0.1297263954621155</v>
       </c>
       <c r="I126" t="n">
-        <v>0.004123312473284965</v>
+        <v>0.003979190089656299</v>
       </c>
     </row>
     <row r="127">
@@ -4105,28 +4105,28 @@
         <v>125</v>
       </c>
       <c r="B127" t="n">
-        <v>0.001259907604008913</v>
+        <v>0.001207800366587937</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0001945814017001539</v>
+        <v>0.0001986474131345749</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1350229742670059</v>
+        <v>0.1291233476753235</v>
       </c>
       <c r="E127" t="n">
-        <v>0.0003902113486658782</v>
+        <v>0.0003635362337864936</v>
       </c>
       <c r="F127" t="n">
-        <v>0.005099417750296741</v>
+        <v>0.005153997251186611</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0002189722419596774</v>
+        <v>0.0001875343831906666</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1336474533396094</v>
+        <v>0.1301802867057856</v>
       </c>
       <c r="I127" t="n">
-        <v>0.004212208198015783</v>
+        <v>0.004315561470446492</v>
       </c>
     </row>
     <row r="128">
@@ -4134,28 +4134,28 @@
         <v>126</v>
       </c>
       <c r="B128" t="n">
-        <v>0.001238743247963488</v>
+        <v>0.001211082916975021</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0001976225674618036</v>
+        <v>0.0001955198145015165</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1343469898691177</v>
+        <v>0.1287839491901398</v>
       </c>
       <c r="E128" t="n">
-        <v>0.0003693857518080622</v>
+        <v>0.0003716433682832867</v>
       </c>
       <c r="F128" t="n">
-        <v>0.00536640678290855</v>
+        <v>0.004705728742417076</v>
       </c>
       <c r="G128" t="n">
-        <v>0.0001926594470505303</v>
+        <v>0.0001850567760628148</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1335509579391697</v>
+        <v>0.1308814398246722</v>
       </c>
       <c r="I128" t="n">
-        <v>0.004505992528160527</v>
+        <v>0.003866264748282208</v>
       </c>
     </row>
     <row r="129">
@@ -4163,28 +4163,28 @@
         <v>127</v>
       </c>
       <c r="B129" t="n">
-        <v>0.001238462102234364</v>
+        <v>0.001208851769074798</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0001961618104008958</v>
+        <v>0.0001922281562220305</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1343705284719467</v>
+        <v>0.129274422006607</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0003704476591665298</v>
+        <v>0.0003702515115141868</v>
       </c>
       <c r="F129" t="n">
-        <v>0.005129438272113707</v>
+        <v>0.005216899649354023</v>
       </c>
       <c r="G129" t="n">
-        <v>0.0001927535683036285</v>
+        <v>0.0002074720765447676</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1334698392448379</v>
+        <v>0.1289813759568076</v>
       </c>
       <c r="I129" t="n">
-        <v>0.004269335538963218</v>
+        <v>0.00436452068260842</v>
       </c>
     </row>
     <row r="130">
@@ -4192,28 +4192,28 @@
         <v>128</v>
       </c>
       <c r="B130" t="n">
-        <v>0.001207763393841684</v>
+        <v>0.001199759256526828</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0001953471660679206</v>
+        <v>0.0001939740038774907</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1339376176214218</v>
+        <v>0.129129796951294</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0003427281462466344</v>
+        <v>0.000360136285442859</v>
       </c>
       <c r="F130" t="n">
-        <v>0.004970817401986964</v>
+        <v>0.004794622652451425</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0001851551215854499</v>
+        <v>0.0001935983010403262</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1340680672906546</v>
+        <v>0.1278480568766399</v>
       </c>
       <c r="I130" t="n">
-        <v>0.004115321958592529</v>
+        <v>0.003961784063730553</v>
       </c>
     </row>
     <row r="131">
@@ -4221,28 +4221,28 @@
         <v>129</v>
       </c>
       <c r="B131" t="n">
-        <v>0.001202125115863979</v>
+        <v>0.001194897584863007</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0001958818084588274</v>
+        <v>0.0001942785780243576</v>
       </c>
       <c r="D131" t="n">
-        <v>0.133956924738884</v>
+        <v>0.1289231120510101</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0003364586992226541</v>
+        <v>0.0003560034695658833</v>
       </c>
       <c r="F131" t="n">
-        <v>0.004952625250337466</v>
+        <v>0.004680418802780778</v>
       </c>
       <c r="G131" t="n">
-        <v>0.0001920830955095346</v>
+        <v>0.0001819624670097136</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1348812166755779</v>
+        <v>0.1297189778099247</v>
       </c>
       <c r="I131" t="n">
-        <v>0.004086136090467406</v>
+        <v>0.003849861412271128</v>
       </c>
     </row>
     <row r="132">
@@ -4250,28 +4250,28 @@
         <v>130</v>
       </c>
       <c r="B132" t="n">
-        <v>0.001190831789851189</v>
+        <v>0.001160035650290549</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0001928536860952154</v>
+        <v>0.0001935110889682546</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1339633162288666</v>
+        <v>0.1287989062385559</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0003281615365799516</v>
+        <v>0.0003225300534609705</v>
       </c>
       <c r="F132" t="n">
-        <v>0.004810379107055812</v>
+        <v>0.005309307581546061</v>
       </c>
       <c r="G132" t="n">
-        <v>0.0001911445406596382</v>
+        <v>0.0002035548878099836</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1332994496841804</v>
+        <v>0.1302387715309712</v>
       </c>
       <c r="I132" t="n">
-        <v>0.003952737330256993</v>
+        <v>0.004454558829049204</v>
       </c>
     </row>
     <row r="133">
@@ -4279,28 +4279,28 @@
         <v>131</v>
       </c>
       <c r="B133" t="n">
-        <v>0.001186178679652512</v>
+        <v>0.001173633526563644</v>
       </c>
       <c r="C133" t="n">
-        <v>0.000191858323821798</v>
+        <v>0.0001910425243601203</v>
       </c>
       <c r="D133" t="n">
-        <v>0.1332987539100647</v>
+        <v>0.1286616226301193</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0003278265954190865</v>
+        <v>0.0003392828993108123</v>
       </c>
       <c r="F133" t="n">
-        <v>0.004838023942182688</v>
+        <v>0.00502596243201082</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0001968574682415841</v>
+        <v>0.00019605519440136</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1334217279721629</v>
+        <v>0.1296324040634986</v>
       </c>
       <c r="I133" t="n">
-        <v>0.003974057832644678</v>
+        <v>0.004181745294542287</v>
       </c>
     </row>
     <row r="134">
@@ -4308,28 +4308,28 @@
         <v>132</v>
       </c>
       <c r="B134" t="n">
-        <v>0.00115663010789454</v>
+        <v>0.001144912047065795</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0001941921435333788</v>
+        <v>0.0001924960686713457</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1334213201665878</v>
+        <v>0.1286884378709793</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0002953313686251641</v>
+        <v>0.0003089738115556538</v>
       </c>
       <c r="F134" t="n">
-        <v>0.004998990390784005</v>
+        <v>0.004973183130696538</v>
       </c>
       <c r="G134" t="n">
-        <v>0.000204409375519197</v>
+        <v>0.000195019140076705</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1343297891982422</v>
+        <v>0.1279608854228482</v>
       </c>
       <c r="I134" t="n">
-        <v>0.004122932068988389</v>
+        <v>0.00413835952581069</v>
       </c>
     </row>
     <row r="135">
@@ -4337,28 +4337,28 @@
         <v>133</v>
       </c>
       <c r="B135" t="n">
-        <v>0.001156106456071138</v>
+        <v>0.001120882637739181</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0001935826570754871</v>
+        <v>0.0001919923458788544</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1328823413505554</v>
+        <v>0.1283627361621857</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0002981121003255248</v>
+        <v>0.0002870766134522855</v>
       </c>
       <c r="F135" t="n">
-        <v>0.004860189755281606</v>
+        <v>0.005169767490626111</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0001794626933828659</v>
+        <v>0.0002004242073837592</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1344909693473315</v>
+        <v>0.1282168071091078</v>
       </c>
       <c r="I135" t="n">
-        <v>0.004008272178797735</v>
+        <v>0.004328259222215531</v>
       </c>
     </row>
     <row r="136">
@@ -4366,28 +4366,28 @@
         <v>134</v>
       </c>
       <c r="B136" t="n">
-        <v>0.001134868975654244</v>
+        <v>0.001126363157041371</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0001927617888692766</v>
+        <v>0.0001904807264497504</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1326134752235412</v>
+        <v>0.1283843189849853</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0002790398196652532</v>
+        <v>0.0002939608460571617</v>
       </c>
       <c r="F136" t="n">
-        <v>0.004992565745047216</v>
+        <v>0.004711799868678775</v>
       </c>
       <c r="G136" t="n">
-        <v>0.000187073444892906</v>
+        <v>0.0001815934804268941</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1332352028886801</v>
+        <v>0.1288540243703817</v>
       </c>
       <c r="I136" t="n">
-        <v>0.004139316351704458</v>
+        <v>0.003885936321626868</v>
       </c>
     </row>
     <row r="137">
@@ -4395,28 +4395,28 @@
         <v>135</v>
       </c>
       <c r="B137" t="n">
-        <v>0.001135560586929321</v>
+        <v>0.001111780429013073</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0001903858581474051</v>
+        <v>0.0001898874953901395</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1326169141044617</v>
+        <v>0.1284430895643234</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0002820901673212647</v>
+        <v>0.0002796774995233863</v>
       </c>
       <c r="F137" t="n">
-        <v>0.005226801687496035</v>
+        <v>0.005086490428151159</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0001919068364499799</v>
+        <v>0.0001975078155080747</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1335697696172005</v>
+        <v>0.128582067588803</v>
       </c>
       <c r="I137" t="n">
-        <v>0.004367045984203892</v>
+        <v>0.004246072338173867</v>
       </c>
     </row>
     <row r="138">
@@ -4424,28 +4424,28 @@
         <v>136</v>
       </c>
       <c r="B138" t="n">
-        <v>0.001115310130149126</v>
+        <v>0.001096398777350783</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0001919943965384737</v>
+        <v>0.0001885811692243442</v>
       </c>
       <c r="D138" t="n">
-        <v>0.1326425532474518</v>
+        <v>0.128222686920166</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0002601029915362596</v>
+        <v>0.0002667041879417375</v>
       </c>
       <c r="F138" t="n">
-        <v>0.005042003543704116</v>
+        <v>0.004743844395074963</v>
       </c>
       <c r="G138" t="n">
-        <v>0.0001897712023096952</v>
+        <v>0.0001894072477962536</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1321390580849002</v>
+        <v>0.1279328233450894</v>
       </c>
       <c r="I138" t="n">
-        <v>0.004191537115261032</v>
+        <v>0.00391477302933753</v>
       </c>
     </row>
     <row r="139">
@@ -4453,28 +4453,28 @@
         <v>137</v>
       </c>
       <c r="B139" t="n">
-        <v>0.001108237557135522</v>
+        <v>0.001090493582606316</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0001897302197562531</v>
+        <v>0.0001894430221663788</v>
       </c>
       <c r="D139" t="n">
-        <v>0.1324722183628082</v>
+        <v>0.1277085339632034</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0002561462546000257</v>
+        <v>0.0002625079087726772</v>
       </c>
       <c r="F139" t="n">
-        <v>0.004967074988206292</v>
+        <v>0.004800595423726283</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0001984654379342751</v>
+        <v>0.0001803181420587805</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1333340015380262</v>
+        <v>0.1277655945555421</v>
       </c>
       <c r="I139" t="n">
-        <v>0.004101939543285582</v>
+        <v>0.003981449269274855</v>
       </c>
     </row>
     <row r="140">
@@ -4482,28 +4482,28 @@
         <v>138</v>
       </c>
       <c r="B140" t="n">
-        <v>0.001099777814462781</v>
+        <v>0.001085736139468849</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0001889113751491532</v>
+        <v>0.0001882361857201904</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1327641295452118</v>
+        <v>0.1278649691820145</v>
       </c>
       <c r="E140" t="n">
-        <v>0.0002470458082295954</v>
+        <v>0.0002581751059088856</v>
       </c>
       <c r="F140" t="n">
-        <v>0.004993856422189884</v>
+        <v>0.004943175166602236</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0001870441410094606</v>
+        <v>0.000182166839120826</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1333012678660148</v>
+        <v>0.1287888250197322</v>
       </c>
       <c r="I140" t="n">
-        <v>0.004140305916123931</v>
+        <v>0.004117064223203923</v>
       </c>
     </row>
     <row r="141">
@@ -4511,28 +4511,28 @@
         <v>139</v>
       </c>
       <c r="B141" t="n">
-        <v>0.001090503445751965</v>
+        <v>0.001075921480834484</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0001899405179182068</v>
+        <v>0.000188375982013531</v>
       </c>
       <c r="D141" t="n">
-        <v>0.1324007148332596</v>
+        <v>0.1280211493253708</v>
       </c>
       <c r="E141" t="n">
-        <v>0.0002385593620482832</v>
+        <v>0.0002474397486653179</v>
       </c>
       <c r="F141" t="n">
-        <v>0.0052102514607057</v>
+        <v>0.004789232569237713</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0001953937933092016</v>
+        <v>0.0001885304355974496</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1320710473766529</v>
+        <v>0.1260955450176998</v>
       </c>
       <c r="I141" t="n">
-        <v>0.004354502447769896</v>
+        <v>0.003970224444054031</v>
       </c>
     </row>
     <row r="142">
@@ -4540,28 +4540,28 @@
         <v>140</v>
       </c>
       <c r="B142" t="n">
-        <v>0.001089604525260627</v>
+        <v>0.001080107739679515</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0001899319144207984</v>
+        <v>0.0001870918904356658</v>
       </c>
       <c r="D142" t="n">
-        <v>0.132247938495636</v>
+        <v>0.1278226158866882</v>
       </c>
       <c r="E142" t="n">
-        <v>0.0002384329144302756</v>
+        <v>0.0002539027664829046</v>
       </c>
       <c r="F142" t="n">
-        <v>0.005017194336623586</v>
+        <v>0.005003827749546405</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0001919540328803194</v>
+        <v>0.0001938841057630624</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1320259606672928</v>
+        <v>0.1279048871323102</v>
       </c>
       <c r="I142" t="n">
-        <v>0.004165110469873247</v>
+        <v>0.004170419219455896</v>
       </c>
     </row>
     <row r="143">
@@ -4569,28 +4569,28 @@
         <v>141</v>
       </c>
       <c r="B143" t="n">
-        <v>0.00107301003087312</v>
+        <v>0.001065045451782644</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0001888169721122831</v>
+        <v>0.0001870799977779388</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1321511635828018</v>
+        <v>0.1279986688985825</v>
       </c>
       <c r="E143" t="n">
-        <v>0.0002234372678268701</v>
+        <v>0.0002379721169108525</v>
       </c>
       <c r="F143" t="n">
-        <v>0.004882479719696096</v>
+        <v>0.004981779811621247</v>
       </c>
       <c r="G143" t="n">
-        <v>0.000179512275749974</v>
+        <v>0.0001923755393373031</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1324879714229173</v>
+        <v>0.12826872335756</v>
       </c>
       <c r="I143" t="n">
-        <v>0.004040527592229294</v>
+        <v>0.004148060745980475</v>
       </c>
     </row>
     <row r="144">
@@ -4598,28 +4598,28 @@
         <v>142</v>
       </c>
       <c r="B144" t="n">
-        <v>0.001070349106103182</v>
+        <v>0.001048664568908513</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0001888039337713271</v>
+        <v>0.0001862577647585422</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1322681589212418</v>
+        <v>0.1277254781131744</v>
       </c>
       <c r="E144" t="n">
-        <v>0.0002202043882198632</v>
+        <v>0.0002237794261360541</v>
       </c>
       <c r="F144" t="n">
-        <v>0.004950169693423378</v>
+        <v>0.004792366291868818</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0001884594994470277</v>
+        <v>0.0001885143323284141</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1322116455926786</v>
+        <v>0.1275577975564058</v>
       </c>
       <c r="I144" t="n">
-        <v>0.004100651992652049</v>
+        <v>0.003966062976986316</v>
       </c>
     </row>
     <row r="145">
@@ -4627,28 +4627,28 @@
         <v>143</v>
       </c>
       <c r="B145" t="n">
-        <v>0.001058362530015409</v>
+        <v>0.001040472563631833</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0001883022343851626</v>
+        <v>0.0001858783301282674</v>
       </c>
       <c r="D145" t="n">
-        <v>0.1318859209184647</v>
+        <v>0.1278127968435288</v>
       </c>
       <c r="E145" t="n">
-        <v>0.0002106307159969583</v>
+        <v>0.0002155302723702043</v>
       </c>
       <c r="F145" t="n">
-        <v>0.004872762724167711</v>
+        <v>0.005046948094352423</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0001863005670447656</v>
+        <v>0.0001824527410380117</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1324765919919504</v>
+        <v>0.128832627670022</v>
       </c>
       <c r="I145" t="n">
-        <v>0.004024079189944229</v>
+        <v>0.004220332164730616</v>
       </c>
     </row>
     <row r="146">
@@ -4656,28 +4656,28 @@
         <v>144</v>
       </c>
       <c r="B146" t="n">
-        <v>0.001051758538722992</v>
+        <v>0.001041092867076397</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0001878049432290718</v>
+        <v>0.0001853614477170631</v>
       </c>
       <c r="D146" t="n">
-        <v>0.1319837006349563</v>
+        <v>0.1277937064161301</v>
       </c>
       <c r="E146" t="n">
-        <v>0.0002040351086817682</v>
+        <v>0.0002167628943193704</v>
       </c>
       <c r="F146" t="n">
-        <v>0.004947489244486608</v>
+        <v>0.004907841071012456</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0001857691186690645</v>
+        <v>0.0001892311298565675</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1325593955617939</v>
+        <v>0.1276773431250555</v>
       </c>
       <c r="I146" t="n">
-        <v>0.004098923177022311</v>
+        <v>0.004080223271358898</v>
       </c>
     </row>
     <row r="147">
@@ -4685,28 +4685,28 @@
         <v>145</v>
       </c>
       <c r="B147" t="n">
-        <v>0.001041083773210645</v>
+        <v>0.001029724780656397</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0001878106359643862</v>
+        <v>0.0001860257305568084</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1320395379962921</v>
+        <v>0.1277101162748337</v>
       </c>
       <c r="E147" t="n">
-        <v>0.0001930754458727315</v>
+        <v>0.0002051484842654318</v>
       </c>
       <c r="F147" t="n">
-        <v>0.004931833148610339</v>
+        <v>0.004753835871602981</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0001899631490650227</v>
+        <v>0.0001824134638634409</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1303305131712318</v>
+        <v>0.1275798194783741</v>
       </c>
       <c r="I147" t="n">
-        <v>0.004090217452626949</v>
+        <v>0.003933523294863825</v>
       </c>
     </row>
     <row r="148">
@@ -4714,28 +4714,28 @@
         <v>146</v>
       </c>
       <c r="B148" t="n">
-        <v>0.001038768381439149</v>
+        <v>0.001017204093240201</v>
       </c>
       <c r="C148" t="n">
-        <v>0.00018811662719585</v>
+        <v>0.0001845895137805492</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1313114780797958</v>
+        <v>0.1274784054479599</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0001940943788895384</v>
+        <v>0.000195222579665482</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00500498372602594</v>
+        <v>0.004891824105095125</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0001862507955568841</v>
+        <v>0.0001841130472649782</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1323839166765306</v>
+        <v>0.1283638207684917</v>
       </c>
       <c r="I148" t="n">
-        <v>0.004156813385697358</v>
+        <v>0.004065891947706654</v>
       </c>
     </row>
     <row r="149">
@@ -4743,28 +4743,28 @@
         <v>147</v>
       </c>
       <c r="B149" t="n">
-        <v>0.001023570198975504</v>
+        <v>0.001015092022068799</v>
       </c>
       <c r="C149" t="n">
-        <v>0.000187960201703012</v>
+        <v>0.0001845407890994102</v>
       </c>
       <c r="D149" t="n">
-        <v>0.1313274381475449</v>
+        <v>0.127705510178566</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0001789728290233761</v>
+        <v>0.000192023697398603</v>
       </c>
       <c r="F149" t="n">
-        <v>0.004816532861304638</v>
+        <v>0.004698641501537253</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0001827175428727748</v>
+        <v>0.0001766701663299623</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1319580678148332</v>
+        <v>0.1286612495872364</v>
       </c>
       <c r="I149" t="n">
-        <v>0.003974025009266825</v>
+        <v>0.003878665089555583</v>
       </c>
     </row>
     <row r="150">
@@ -4772,28 +4772,28 @@
         <v>148</v>
       </c>
       <c r="B150" t="n">
-        <v>0.001015558969110251</v>
+        <v>0.001008615428581834</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0001868542443979532</v>
+        <v>0.0001832219303632155</v>
       </c>
       <c r="D150" t="n">
-        <v>0.1312241425924301</v>
+        <v>0.1278449190378189</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0001725840206798166</v>
+        <v>0.0001861689052730799</v>
       </c>
       <c r="F150" t="n">
-        <v>0.004903590770265115</v>
+        <v>0.00495569947204548</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0001853627149227606</v>
+        <v>0.0001823252354314411</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1307690215596951</v>
+        <v>0.1279554191392164</v>
       </c>
       <c r="I150" t="n">
-        <v>0.00406438294497317</v>
+        <v>0.004133597185674198</v>
       </c>
     </row>
     <row r="151">
@@ -4801,28 +4801,28 @@
         <v>149</v>
       </c>
       <c r="B151" t="n">
-        <v>0.001013149112954736</v>
+        <v>0.000998382815681398</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0001860932492753491</v>
+        <v>0.0001831290110340342</v>
       </c>
       <c r="D151" t="n">
-        <v>0.1312753278312683</v>
+        <v>0.1279029739923477</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0001706792499246076</v>
+        <v>0.0001757389540728182</v>
       </c>
       <c r="F151" t="n">
-        <v>0.005049788963329199</v>
+        <v>0.004662795014843515</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0001860422714733782</v>
+        <v>0.0001887668796217139</v>
       </c>
       <c r="H151" t="n">
-        <v>0.131641023600471</v>
+        <v>0.1268998411730491</v>
       </c>
       <c r="I151" t="n">
-        <v>0.004205541598229239</v>
+        <v>0.003839528959982863</v>
       </c>
     </row>
     <row r="152">
@@ -4830,28 +4830,28 @@
         <v>150</v>
       </c>
       <c r="B152" t="n">
-        <v>0.001005223943904042</v>
+        <v>0.0009983256779164077</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0001854817960327491</v>
+        <v>0.0001821854136949405</v>
       </c>
       <c r="D152" t="n">
-        <v>0.1312785622930527</v>
+        <v>0.1278564500303268</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0001633493473622948</v>
+        <v>0.000176858037176542</v>
       </c>
       <c r="F152" t="n">
-        <v>0.004872732669886864</v>
+        <v>0.004937639307856657</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0001849905620150566</v>
+        <v>0.00019322455354752</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1312537441109755</v>
+        <v>0.1265693951674037</v>
       </c>
       <c r="I152" t="n">
-        <v>0.004031473371408406</v>
+        <v>0.00411156774895056</v>
       </c>
     </row>
     <row r="153">
@@ -4859,28 +4859,28 @@
         <v>151</v>
       </c>
       <c r="B153" t="n">
-        <v>0.001002945707015693</v>
+        <v>0.0009972668530493975</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0001848658552849665</v>
+        <v>0.0001836417211592197</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1313773642501831</v>
+        <v>0.1276959649324417</v>
       </c>
       <c r="E153" t="n">
-        <v>0.0001611930517163128</v>
+        <v>0.0001751453234627843</v>
       </c>
       <c r="F153" t="n">
-        <v>0.004931148688596039</v>
+        <v>0.004760321033191768</v>
       </c>
       <c r="G153" t="n">
-        <v>0.0001879515993993024</v>
+        <v>0.0001868917725189873</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1316182128377684</v>
+        <v>0.1274858645669399</v>
       </c>
       <c r="I153" t="n">
-        <v>0.004085106027067972</v>
+        <v>0.003935999939063196</v>
       </c>
     </row>
     <row r="154">
@@ -4888,28 +4888,28 @@
         <v>152</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0009988880460634827</v>
+        <v>0.0009844642691612243</v>
       </c>
       <c r="C154" t="n">
-        <v>0.000185413326616399</v>
+        <v>0.0001832559651173651</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1313689578933716</v>
+        <v>0.1275131684436798</v>
       </c>
       <c r="E154" t="n">
-        <v>0.0001566299405014143</v>
+        <v>0.0001636424744809046</v>
       </c>
       <c r="F154" t="n">
-        <v>0.004978714447216317</v>
+        <v>0.004900643809730427</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0001914172008847073</v>
+        <v>0.000192535026780433</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1314375503067091</v>
+        <v>0.1272998370655598</v>
       </c>
       <c r="I154" t="n">
-        <v>0.004130109488116319</v>
+        <v>0.004071609638479416</v>
       </c>
     </row>
     <row r="155">
@@ -4917,28 +4917,28 @@
         <v>153</v>
       </c>
       <c r="B155" t="n">
-        <v>0.000989854415409267</v>
+        <v>0.0009827129728645085</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0001847013868447393</v>
+        <v>0.0001821954937046394</v>
       </c>
       <c r="D155" t="n">
-        <v>0.131326160946846</v>
+        <v>0.1276805312986374</v>
       </c>
       <c r="E155" t="n">
-        <v>0.0001485222376091406</v>
+        <v>0.0001621148411687464</v>
       </c>
       <c r="F155" t="n">
-        <v>0.005011834000065607</v>
+        <v>0.004769422372265264</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0001840568841894599</v>
+        <v>0.0001773729147592736</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1322356435593345</v>
+        <v>0.1284699426146549</v>
       </c>
       <c r="I155" t="n">
-        <v>0.004166598871204437</v>
+        <v>0.003949699779550072</v>
       </c>
     </row>
     <row r="156">
@@ -4946,28 +4946,28 @@
         <v>154</v>
       </c>
       <c r="B156" t="n">
-        <v>0.0009878718503788114</v>
+        <v>0.0009697950452715159</v>
       </c>
       <c r="C156" t="n">
-        <v>0.000184066842501983</v>
+        <v>0.0001813892595916986</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1315235892658234</v>
+        <v>0.1276432113513946</v>
       </c>
       <c r="E156" t="n">
-        <v>0.0001461870796512812</v>
+        <v>0.0001501897508418187</v>
       </c>
       <c r="F156" t="n">
-        <v>0.00484466397484573</v>
+        <v>0.004837311148631339</v>
       </c>
       <c r="G156" t="n">
-        <v>0.000181969655822958</v>
+        <v>0.000184344880895911</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1317865826323215</v>
+        <v>0.1278252904897413</v>
       </c>
       <c r="I156" t="n">
-        <v>0.004003761408145602</v>
+        <v>0.004013839767240048</v>
       </c>
     </row>
     <row r="157">
@@ -4975,28 +4975,28 @@
         <v>155</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0009855675634108485</v>
+        <v>0.0009706554818227888</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0001848313776226714</v>
+        <v>0.0001809768242798746</v>
       </c>
       <c r="D157" t="n">
-        <v>0.1311790099067688</v>
+        <v>0.1279378952589035</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0001448411582298577</v>
+        <v>0.0001499891983782872</v>
       </c>
       <c r="F157" t="n">
-        <v>0.004951590040172975</v>
+        <v>0.004893509614331493</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0001849607507981965</v>
+        <v>0.0001807943016095436</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1313502375599222</v>
+        <v>0.1284037221003123</v>
       </c>
       <c r="I157" t="n">
-        <v>0.004109878129588644</v>
+        <v>0.004070696732785923</v>
       </c>
     </row>
     <row r="158">
@@ -5004,28 +5004,28 @@
         <v>156</v>
       </c>
       <c r="B158" t="n">
-        <v>0.000979366682499647</v>
+        <v>0.0009668502092920244</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0001844983292901888</v>
+        <v>0.0001805770540740341</v>
       </c>
       <c r="D158" t="n">
-        <v>0.131160180138588</v>
+        <v>0.1280303380765915</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0001390674568833783</v>
+        <v>0.000146121479739435</v>
       </c>
       <c r="F158" t="n">
-        <v>0.004844735580728941</v>
+        <v>0.004702023386918799</v>
       </c>
       <c r="G158" t="n">
-        <v>0.0001812505355745943</v>
+        <v>0.0001824330380382047</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1313050632288172</v>
+        <v>0.1275010295326519</v>
       </c>
       <c r="I158" t="n">
-        <v>0.004006959721233337</v>
+        <v>0.003882085199985915</v>
       </c>
     </row>
     <row r="159">
@@ -5033,28 +5033,28 @@
         <v>157</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0009775835584253073</v>
+        <v>0.0009599312806129456</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0001837982967300341</v>
+        <v>0.0001810652082953602</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1313210719995499</v>
+        <v>0.1278452481861115</v>
       </c>
       <c r="E159" t="n">
-        <v>0.0001371799099766649</v>
+        <v>0.0001396398484418169</v>
       </c>
       <c r="F159" t="n">
-        <v>0.004933848366092702</v>
+        <v>0.004907764060191847</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0001865757769201601</v>
+        <v>0.0001794808584413161</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1309728166582534</v>
+        <v>0.1282444635592705</v>
       </c>
       <c r="I159" t="n">
-        <v>0.004092408504343149</v>
+        <v>0.004087060910587307</v>
       </c>
     </row>
     <row r="160">
@@ -5062,28 +5062,28 @@
         <v>158</v>
       </c>
       <c r="B160" t="n">
-        <v>0.000974495990101248</v>
+        <v>0.0009608822100386023</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0001836028100987896</v>
+        <v>0.0001796125142853707</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1312944598722458</v>
+        <v>0.1280709173488617</v>
       </c>
       <c r="E160" t="n">
-        <v>0.0001344208963704295</v>
+        <v>0.0001409151251334697</v>
       </c>
       <c r="F160" t="n">
-        <v>0.004790022407596108</v>
+        <v>0.004791381876235053</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0001836033829430507</v>
+        <v>0.0001813750816406576</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1310866479325256</v>
+        <v>0.1276919748615868</v>
       </c>
       <c r="I160" t="n">
-        <v>0.003950985758086791</v>
+        <v>0.003971546887865269</v>
       </c>
     </row>
     <row r="161">
@@ -5091,28 +5091,28 @@
         <v>159</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0009654731393456459</v>
+        <v>0.000954893591761589</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0001840553107755259</v>
+        <v>0.000180061595082283</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1312004532604218</v>
+        <v>0.12807258751297</v>
       </c>
       <c r="E161" t="n">
-        <v>0.0001254155693538487</v>
+        <v>0.0001344690858069807</v>
       </c>
       <c r="F161" t="n">
-        <v>0.004924054408588768</v>
+        <v>0.004700360295422023</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0001834963943177248</v>
+        <v>0.0001773134383954469</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1317160473056563</v>
+        <v>0.1287276753720024</v>
       </c>
       <c r="I161" t="n">
-        <v>0.004081977816210485</v>
+        <v>0.003879408471675234</v>
       </c>
     </row>
     <row r="162">
@@ -5120,28 +5120,28 @@
         <v>160</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0009648172153867782</v>
+        <v>0.0009508713543117046</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0001831166830286384</v>
+        <v>0.0001796053460845724</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1313010226125717</v>
+        <v>0.1280518296480179</v>
       </c>
       <c r="E162" t="n">
-        <v>0.0001251954371272586</v>
+        <v>0.0001310068707671017</v>
       </c>
       <c r="F162" t="n">
-        <v>0.004885088775373789</v>
+        <v>0.004838835607156717</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0001868876640760487</v>
+        <v>0.000181603581388405</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1302730238923824</v>
+        <v>0.1282588572078195</v>
       </c>
       <c r="I162" t="n">
-        <v>0.00404683594742325</v>
+        <v>0.004015937749095881</v>
       </c>
     </row>
     <row r="163">
@@ -5149,28 +5149,28 @@
         <v>161</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0009614319793917239</v>
+        <v>0.0009491621984988451</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0001834391426909715</v>
+        <v>0.0001798627522187308</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1312369034500122</v>
+        <v>0.1279814335289002</v>
       </c>
       <c r="E163" t="n">
-        <v>0.000121808327042032</v>
+        <v>0.0001293922929763794</v>
       </c>
       <c r="F163" t="n">
-        <v>0.004941146095293964</v>
+        <v>0.004795171044596743</v>
       </c>
       <c r="G163" t="n">
-        <v>0.000186218830037461</v>
+        <v>0.0001784109593348936</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1308032928069303</v>
+        <v>0.1281853334685912</v>
       </c>
       <c r="I163" t="n">
-        <v>0.004100910786852289</v>
+        <v>0.003975833388877999</v>
       </c>
     </row>
     <row r="164">
@@ -5178,28 +5178,28 @@
         <v>162</v>
       </c>
       <c r="B164" t="n">
-        <v>0.000959058281738311</v>
+        <v>0.0009434897845163942</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0001834005440790206</v>
+        <v>0.0001789936891673133</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1311551138010025</v>
+        <v>0.1282070340862274</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0001198821778120473</v>
+        <v>0.0001234609375270084</v>
       </c>
       <c r="F164" t="n">
-        <v>0.004895870737840846</v>
+        <v>0.004756828177534956</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0001829475277628777</v>
+        <v>0.0001804013130398236</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1315339024518092</v>
+        <v>0.1277572551821807</v>
       </c>
       <c r="I164" t="n">
-        <v>0.004055253699920209</v>
+        <v>0.003937640588283903</v>
       </c>
     </row>
     <row r="165">
@@ -5207,28 +5207,28 @@
         <v>163</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0009545501920245588</v>
+        <v>0.0009424930441081524</v>
       </c>
       <c r="C165" t="n">
-        <v>0.000183028346337378</v>
+        <v>0.000179028787786141</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1311094596004486</v>
+        <v>0.1281322485551834</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0001159745617518201</v>
+        <v>0.0001228030293658376</v>
       </c>
       <c r="F165" t="n">
-        <v>0.005015747675164732</v>
+        <v>0.004868816196201385</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0001817013722641977</v>
+        <v>0.0001796628613302979</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1314592779888414</v>
+        <v>0.1279429272862476</v>
       </c>
       <c r="I165" t="n">
-        <v>0.004176749971681571</v>
+        <v>0.004049438650204783</v>
       </c>
     </row>
     <row r="166">
@@ -5236,28 +5236,28 @@
         <v>164</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0009538621250763536</v>
+        <v>0.0009433778142780066</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0001829684820501134</v>
+        <v>0.0001791843186458573</v>
       </c>
       <c r="D166" t="n">
-        <v>0.1311713732337952</v>
+        <v>0.1280460443468094</v>
       </c>
       <c r="E166" t="n">
-        <v>0.000115036789746955</v>
+        <v>0.0001239632862103172</v>
       </c>
       <c r="F166" t="n">
-        <v>0.004843336092991843</v>
+        <v>0.004764133160797116</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0001850080892314898</v>
+        <v>0.0001785189383194158</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1305530445367633</v>
+        <v>0.1284189986239444</v>
       </c>
       <c r="I166" t="n">
-        <v>0.004005562782129592</v>
+        <v>0.003943519248106011</v>
       </c>
     </row>
     <row r="167">
@@ -5265,28 +5265,28 @@
         <v>165</v>
       </c>
       <c r="B167" t="n">
-        <v>0.0009500058209598064</v>
+        <v>0.0009387825296521187</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0001824491836177185</v>
+        <v>0.0001789041139101609</v>
       </c>
       <c r="D167" t="n">
-        <v>0.1311136549558639</v>
+        <v>0.1281166369800568</v>
       </c>
       <c r="E167" t="n">
-        <v>0.0001119883690522984</v>
+        <v>0.0001192952482830733</v>
       </c>
       <c r="F167" t="n">
-        <v>0.004905271182082849</v>
+        <v>0.004841094752606521</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0001809467848469724</v>
+        <v>0.000176876524801717</v>
       </c>
       <c r="H167" t="n">
-        <v>0.131735267038252</v>
+        <v>0.1285138136624901</v>
       </c>
       <c r="I167" t="n">
-        <v>0.004065648018326276</v>
+        <v>0.004021649224012117</v>
       </c>
     </row>
     <row r="168">
@@ -5294,28 +5294,28 @@
         <v>166</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0009474950637742877</v>
+        <v>0.0009335334090664983</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0001825627053137869</v>
+        <v>0.0001789874773183838</v>
       </c>
       <c r="D168" t="n">
-        <v>0.131187445895195</v>
+        <v>0.1280900391578674</v>
       </c>
       <c r="E168" t="n">
-        <v>0.000108995147020556</v>
+        <v>0.0001140957406917587</v>
       </c>
       <c r="F168" t="n">
-        <v>0.004867992789543813</v>
+        <v>0.004757064009149108</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0001836964153216735</v>
+        <v>0.0001791518910069757</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1306965345562379</v>
+        <v>0.1280114601593811</v>
       </c>
       <c r="I168" t="n">
-        <v>0.004030813736321487</v>
+        <v>0.003937854848644084</v>
       </c>
     </row>
     <row r="169">
@@ -5323,28 +5323,28 @@
         <v>167</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0009444226300343871</v>
+        <v>0.0009320232124552131</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0001826134446701035</v>
+        <v>0.0001779112998619676</v>
       </c>
       <c r="D169" t="n">
-        <v>0.1310725190534592</v>
+        <v>0.1282256681404114</v>
       </c>
       <c r="E169" t="n">
-        <v>0.0001064465997312218</v>
+        <v>0.0001129835867281072</v>
       </c>
       <c r="F169" t="n">
-        <v>0.004871856025002326</v>
+        <v>0.004860696411322419</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0001785394288973615</v>
+        <v>0.0001801561134457922</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1320012066832958</v>
+        <v>0.1278547467444499</v>
       </c>
       <c r="I169" t="n">
-        <v>0.004033310562797608</v>
+        <v>0.004041266593334628</v>
       </c>
     </row>
     <row r="170">
@@ -5352,28 +5352,28 @@
         <v>168</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0009443914181776345</v>
+        <v>0.0009298643715903163</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0001819339972250164</v>
+        <v>0.0001777435871539638</v>
       </c>
       <c r="D170" t="n">
-        <v>0.1311724249258041</v>
+        <v>0.1282682597389221</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0001065953077995218</v>
+        <v>0.000110779510082677</v>
       </c>
       <c r="F170" t="n">
-        <v>0.004965008070774462</v>
+        <v>0.004771138949693465</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0001865888620763987</v>
+        <v>0.0001779439492507414</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1302021455307769</v>
+        <v>0.1282009240066052</v>
       </c>
       <c r="I170" t="n">
-        <v>0.004127408515336828</v>
+        <v>0.003952190413764187</v>
       </c>
     </row>
     <row r="171">
@@ -5381,28 +5381,28 @@
         <v>169</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0009413806291595101</v>
+        <v>0.0009259187904559076</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0001823757296064869</v>
+        <v>0.0001779272074680775</v>
       </c>
       <c r="D171" t="n">
-        <v>0.131056490439415</v>
+        <v>0.1282548932590485</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0001037224608650431</v>
+        <v>0.000106717124489136</v>
       </c>
       <c r="F171" t="n">
-        <v>0.004909215535221053</v>
+        <v>0.004748096958769038</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0001825900143211811</v>
+        <v>0.0001781932145387897</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1308608239616889</v>
+        <v>0.1281186440202968</v>
       </c>
       <c r="I171" t="n">
-        <v>0.004072321419304823</v>
+        <v>0.003929310503383858</v>
       </c>
     </row>
     <row r="172">
@@ -5410,28 +5410,28 @@
         <v>170</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0009392511167377233</v>
+        <v>0.0009257651666589081</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0001815182518372312</v>
+        <v>0.0001777823138767853</v>
       </c>
       <c r="D172" t="n">
-        <v>0.1311557137575149</v>
+        <v>0.1282303496704102</v>
       </c>
       <c r="E172" t="n">
-        <v>0.000101954310907051</v>
+        <v>0.0001068311123596504</v>
       </c>
       <c r="F172" t="n">
-        <v>0.004879698848525035</v>
+        <v>0.004873813117260256</v>
       </c>
       <c r="G172" t="n">
-        <v>0.000182506574630596</v>
+        <v>0.0001781200287040539</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1311010407088826</v>
+        <v>0.1281830909289116</v>
       </c>
       <c r="I172" t="n">
-        <v>0.004041687155151542</v>
+        <v>0.00405477762948509</v>
       </c>
     </row>
     <row r="173">
@@ -5439,28 +5439,28 @@
         <v>171</v>
       </c>
       <c r="B173" t="n">
-        <v>0.000937805431485176</v>
+        <v>0.0009255574317127466</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0001816340767722577</v>
+        <v>0.0001771935806525871</v>
       </c>
       <c r="D173" t="n">
-        <v>0.1311999839019775</v>
+        <v>0.1284072686071396</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001001714392574504</v>
+        <v>0.0001063275199993514</v>
       </c>
       <c r="F173" t="n">
-        <v>0.004887636887307657</v>
+        <v>0.00481666632428109</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0001834637921337315</v>
+        <v>0.0001791491834106848</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1307753786896804</v>
+        <v>0.1279101083922347</v>
       </c>
       <c r="I173" t="n">
-        <v>0.004050296237889744</v>
+        <v>0.003997966635267312</v>
       </c>
     </row>
     <row r="174">
@@ -5468,28 +5468,28 @@
         <v>172</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0009345085218325258</v>
+        <v>0.0009213235200569034</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0001820074824709445</v>
+        <v>0.0001775062844268978</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1310824935674667</v>
+        <v>0.1282844614439011</v>
       </c>
       <c r="E174" t="n">
-        <v>9.70885887434706e-05</v>
+        <v>0.0001023949437732808</v>
       </c>
       <c r="F174" t="n">
-        <v>0.004813934011023255</v>
+        <v>0.004787492387355298</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0001815777875683962</v>
+        <v>0.0001782011041228947</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1310763497541235</v>
+        <v>0.1281962197464792</v>
       </c>
       <c r="I174" t="n">
-        <v>0.003976974535010281</v>
+        <v>0.003968310204059566</v>
       </c>
     </row>
     <row r="175">
@@ -5497,28 +5497,28 @@
         <v>173</v>
       </c>
       <c r="B175" t="n">
-        <v>0.000934521018922329</v>
+        <v>0.000921324728898704</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0001817988674631342</v>
+        <v>0.0001774036639519036</v>
       </c>
       <c r="D175" t="n">
-        <v>0.1310814369602203</v>
+        <v>0.1283564522771835</v>
       </c>
       <c r="E175" t="n">
-        <v>9.7314976436086e-05</v>
+        <v>0.000102138818172738</v>
       </c>
       <c r="F175" t="n">
-        <v>0.004838844634635073</v>
+        <v>0.004775541621255787</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0001804943877733031</v>
+        <v>0.0001776478877551261</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1312485910852426</v>
+        <v>0.1283315661875303</v>
       </c>
       <c r="I175" t="n">
-        <v>0.004002107334753186</v>
+        <v>0.003956235988737125</v>
       </c>
     </row>
     <row r="176">
@@ -5526,28 +5526,28 @@
         <v>174</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0009318805301599205</v>
+        <v>0.0009192845804058016</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0001817214812664315</v>
+        <v>0.0001774002145081758</v>
       </c>
       <c r="D176" t="n">
-        <v>0.1310087673311233</v>
+        <v>0.1282973584156036</v>
       </c>
       <c r="E176" t="n">
-        <v>9.511522175325081e-05</v>
+        <v>0.0001003975939406082</v>
       </c>
       <c r="F176" t="n">
-        <v>0.004876494353536826</v>
+        <v>0.004793745922973018</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0001807885869684573</v>
+        <v>0.0001775163027049964</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1311395594793665</v>
+        <v>0.1282725957770137</v>
       </c>
       <c r="I176" t="n">
-        <v>0.004040007887569181</v>
+        <v>0.003974866639840953</v>
       </c>
     </row>
     <row r="177">
@@ -5555,28 +5555,28 @@
         <v>175</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0009318855435103178</v>
+        <v>0.0009195149039328099</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0001814062140304595</v>
+        <v>0.0001771206523291767</v>
       </c>
       <c r="D177" t="n">
-        <v>0.1310800731906891</v>
+        <v>0.1283136093921661</v>
       </c>
       <c r="E177" t="n">
-        <v>9.507898024702445e-05</v>
+        <v>0.0001008262159917504</v>
       </c>
       <c r="F177" t="n">
-        <v>0.004906576727235881</v>
+        <v>0.004780271481054107</v>
       </c>
       <c r="G177" t="n">
-        <v>0.0001821205920640829</v>
+        <v>0.0001756858648534797</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1308282552467474</v>
+        <v>0.1285868782689871</v>
       </c>
       <c r="I177" t="n">
-        <v>0.004070314838023792</v>
+        <v>0.003961651210428548</v>
       </c>
     </row>
     <row r="178">
@@ -5584,28 +5584,28 @@
         <v>176</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0009292679332122207</v>
+        <v>0.0009184085736498236</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0001809607507139444</v>
+        <v>0.0001769308144021779</v>
       </c>
       <c r="D178" t="n">
-        <v>0.1310828272056579</v>
+        <v>0.1283769686136246</v>
       </c>
       <c r="E178" t="n">
-        <v>9.289306057617069e-05</v>
+        <v>9.959293260984123e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>0.004844659337375866</v>
+        <v>0.004758899426558716</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0001820266300929728</v>
+        <v>0.0001762358765486251</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1308621282571681</v>
+        <v>0.128510058835319</v>
       </c>
       <c r="I178" t="n">
-        <v>0.004008322052481367</v>
+        <v>0.003940113205447501</v>
       </c>
     </row>
     <row r="179">
@@ -5613,28 +5613,28 @@
         <v>177</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0009294326651580632</v>
+        <v>0.0009169622586593032</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0001814903981992975</v>
+        <v>0.0001767333269482478</v>
       </c>
       <c r="D179" t="n">
-        <v>0.1309898539476395</v>
+        <v>0.1284464428186417</v>
       </c>
       <c r="E179" t="n">
-        <v>9.299300311645492e-05</v>
+        <v>9.799672603467479e-05</v>
       </c>
       <c r="F179" t="n">
-        <v>0.004892837048324393</v>
+        <v>0.0047762587586749</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0001817355191997491</v>
+        <v>0.0001786159514981287</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1308633760993671</v>
+        <v>0.1279599356748541</v>
       </c>
       <c r="I179" t="n">
-        <v>0.004056784740951501</v>
+        <v>0.003957843127862518</v>
       </c>
     </row>
     <row r="180">
@@ -5642,28 +5642,28 @@
         <v>178</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0009287040021866561</v>
+        <v>0.0009146777030527592</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0001813626777296886</v>
+        <v>0.0001770056342594326</v>
       </c>
       <c r="D180" t="n">
-        <v>0.1309772851324081</v>
+        <v>0.128379901304245</v>
       </c>
       <c r="E180" t="n">
-        <v>9.245490953139961e-05</v>
+        <v>9.577259448496625e-05</v>
       </c>
       <c r="F180" t="n">
-        <v>0.004855487186090982</v>
+        <v>0.00478822993318175</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001816405085791707</v>
+        <v>0.000176593305890222</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1308908950028178</v>
+        <v>0.1283568743430382</v>
       </c>
       <c r="I180" t="n">
-        <v>0.004019392132303308</v>
+        <v>0.00396985226880522</v>
       </c>
     </row>
     <row r="181">
@@ -5671,28 +5671,28 @@
         <v>179</v>
       </c>
       <c r="B181" t="n">
-        <v>0.000926883108817041</v>
+        <v>0.0009152874501571059</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0001812671679481864</v>
+        <v>0.0001772730328096077</v>
       </c>
       <c r="D181" t="n">
-        <v>0.1309898828763962</v>
+        <v>0.1283207310342789</v>
       </c>
       <c r="E181" t="n">
-        <v>9.066653720568865e-05</v>
+        <v>9.641077354643494e-05</v>
       </c>
       <c r="F181" t="n">
-        <v>0.004838604613938057</v>
+        <v>0.00478206166854739</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0001810872271735993</v>
+        <v>0.000176066256150661</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1310487147227392</v>
+        <v>0.1284922409397937</v>
       </c>
       <c r="I181" t="n">
-        <v>0.004002273847086152</v>
+        <v>0.003963534251770057</v>
       </c>
     </row>
     <row r="182">
@@ -5700,28 +5700,28 @@
         <v>180</v>
       </c>
       <c r="B182" t="n">
-        <v>0.000927020987175405</v>
+        <v>0.0009136760801002383</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0001811235914248973</v>
+        <v>0.0001767367382384837</v>
       </c>
       <c r="D182" t="n">
-        <v>0.1309953983602524</v>
+        <v>0.1284337925920487</v>
       </c>
       <c r="E182" t="n">
-        <v>9.092042856151239e-05</v>
+        <v>9.477039951644838e-05</v>
       </c>
       <c r="F182" t="n">
-        <v>0.00487062768448527</v>
+        <v>0.004775182076655389</v>
       </c>
       <c r="G182" t="n">
-        <v>0.000180953605291183</v>
+        <v>0.0001772065464328203</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1309755846542013</v>
+        <v>0.128256289775181</v>
       </c>
       <c r="I182" t="n">
-        <v>0.004034796199513687</v>
+        <v>0.003956694134509534</v>
       </c>
     </row>
     <row r="183">
@@ -5729,28 +5729,28 @@
         <v>181</v>
       </c>
       <c r="B183" t="n">
-        <v>0.0009252277080379427</v>
+        <v>0.000913015677139163</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0001810691847465932</v>
+        <v>0.0001763645737878978</v>
       </c>
       <c r="D183" t="n">
-        <v>0.1309958091850281</v>
+        <v>0.1285261941728592</v>
       </c>
       <c r="E183" t="n">
-        <v>8.917949441866949e-05</v>
+        <v>9.40201469277963e-05</v>
       </c>
       <c r="F183" t="n">
-        <v>0.004855795816972633</v>
+        <v>0.00478941547008289</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0001813900591953708</v>
+        <v>0.000176166710941361</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1308859612356391</v>
+        <v>0.1284706618356082</v>
       </c>
       <c r="I183" t="n">
-        <v>0.004019975915162248</v>
+        <v>0.003970895479121785</v>
       </c>
     </row>
     <row r="184">
@@ -5758,28 +5758,28 @@
         <v>182</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0009237556477710605</v>
+        <v>0.0009123249152377247</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0001810396328000352</v>
+        <v>0.0001766382354889065</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1309983833293915</v>
+        <v>0.1284295295181274</v>
       </c>
       <c r="E184" t="n">
-        <v>8.772411288227886e-05</v>
+        <v>9.35390387121588e-05</v>
       </c>
       <c r="F184" t="n">
-        <v>0.004876919105606455</v>
+        <v>0.004793930706669855</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0001801457848875794</v>
+        <v>0.0001765421105565452</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1311438035332943</v>
+        <v>0.1284494697823999</v>
       </c>
       <c r="I184" t="n">
-        <v>0.004041054321051884</v>
+        <v>0.003975141235364398</v>
       </c>
     </row>
     <row r="185">
@@ -5787,28 +5787,28 @@
         <v>183</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0009243037064373493</v>
+        <v>0.0009128978805877268</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0001806958843143657</v>
+        <v>0.0001767713676476851</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1310413145933151</v>
+        <v>0.1284353232717514</v>
       </c>
       <c r="E185" t="n">
-        <v>8.840125473309308e-05</v>
+        <v>9.394991062721238e-05</v>
       </c>
       <c r="F185" t="n">
-        <v>0.004873217480928678</v>
+        <v>0.004800488886348964</v>
       </c>
       <c r="G185" t="n">
-        <v>0.0001807982106110063</v>
+        <v>0.0001766724915731376</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1309881038971087</v>
+        <v>0.1284058470263178</v>
       </c>
       <c r="I185" t="n">
-        <v>0.004037478802069341</v>
+        <v>0.003981787162797972</v>
       </c>
     </row>
     <row r="186">
@@ -5816,28 +5816,28 @@
         <v>184</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0009235302403718233</v>
+        <v>0.0009099145712740719</v>
       </c>
       <c r="C186" t="n">
-        <v>0.000180836464708671</v>
+        <v>0.0001769134911410511</v>
       </c>
       <c r="D186" t="n">
-        <v>0.1309998589086533</v>
+        <v>0.1283998211994171</v>
       </c>
       <c r="E186" t="n">
-        <v>8.76944966041483e-05</v>
+        <v>9.100197753217071e-05</v>
       </c>
       <c r="F186" t="n">
-        <v>0.004859892998261416</v>
+        <v>0.004780791711098656</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0001812178734993808</v>
+        <v>0.0001766687111270448</v>
       </c>
       <c r="H186" t="n">
-        <v>0.13077768612258</v>
+        <v>0.1283801392036783</v>
       </c>
       <c r="I186" t="n">
-        <v>0.004024786669700171</v>
+        <v>0.003962222313429389</v>
       </c>
     </row>
     <row r="187">
@@ -5845,28 +5845,28 @@
         <v>185</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0009228167965263128</v>
+        <v>0.0009108735080882907</v>
       </c>
       <c r="C187" t="n">
-        <v>0.000180941000521183</v>
+        <v>0.0001764503245474771</v>
       </c>
       <c r="D187" t="n">
-        <v>0.1309657233037949</v>
+        <v>0.1284570404806137</v>
       </c>
       <c r="E187" t="n">
-        <v>8.704720285069197e-05</v>
+        <v>9.213799389218912e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>0.004872780343210766</v>
+        <v>0.004773096249972092</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0001806920506586176</v>
+        <v>0.0001760806749023339</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1309535913551029</v>
+        <v>0.1285033609388703</v>
       </c>
       <c r="I187" t="n">
-        <v>0.004037320336804012</v>
+        <v>0.003954498784367427</v>
       </c>
     </row>
     <row r="188">
@@ -5874,28 +5874,28 @@
         <v>186</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0009224218699038028</v>
+        <v>0.0009095409309044481</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0001807647706577554</v>
+        <v>0.0001765577160557732</v>
       </c>
       <c r="D188" t="n">
-        <v>0.1310279388399124</v>
+        <v>0.1284402802352905</v>
       </c>
       <c r="E188" t="n">
-        <v>8.651741566695273e-05</v>
+        <v>9.078182436712087e-05</v>
       </c>
       <c r="F188" t="n">
-        <v>0.00487633050317598</v>
+        <v>0.004794248456794763</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0001809092915805321</v>
+        <v>0.0001772259725303333</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1309236977141211</v>
+        <v>0.1282594886242274</v>
       </c>
       <c r="I188" t="n">
-        <v>0.004040802746667826</v>
+        <v>0.003975724985497908</v>
       </c>
     </row>
     <row r="189">
@@ -5903,28 +5903,28 @@
         <v>187</v>
       </c>
       <c r="B189" t="n">
-        <v>0.0009222484073229134</v>
+        <v>0.0009102265316620469</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0001806545835360885</v>
+        <v>0.0001768132215794176</v>
       </c>
       <c r="D189" t="n">
-        <v>0.1310065717449188</v>
+        <v>0.1283768458442688</v>
       </c>
       <c r="E189" t="n">
-        <v>8.656097563588992e-05</v>
+        <v>9.15291020963341e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.00490371241892094</v>
+        <v>0.004759840085634545</v>
       </c>
       <c r="G189" t="n">
-        <v>0.0001806336872765436</v>
+        <v>0.0001769739923572174</v>
       </c>
       <c r="H189" t="n">
-        <v>0.130981717157325</v>
+        <v>0.1283280880873199</v>
       </c>
       <c r="I189" t="n">
-        <v>0.004068170187517782</v>
+        <v>0.003941225682447556</v>
       </c>
     </row>
     <row r="190">
@@ -5932,28 +5932,28 @@
         <v>188</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0009225863895863294</v>
+        <v>0.0009095480301603675</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0001809762311773375</v>
+        <v>0.0001766734859151766</v>
       </c>
       <c r="D190" t="n">
-        <v>0.1309472682161331</v>
+        <v>0.1284193686609268</v>
       </c>
       <c r="E190" t="n">
-        <v>8.687382485391573e-05</v>
+        <v>9.07777190161869e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.004878997981675929</v>
+        <v>0.004779990232134842</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0001805583570136569</v>
+        <v>0.0001766647751981295</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1309587074590157</v>
+        <v>0.128353693845027</v>
       </c>
       <c r="I190" t="n">
-        <v>0.004043646134302433</v>
+        <v>0.003961556941197902</v>
       </c>
     </row>
     <row r="191">
@@ -5961,28 +5961,28 @@
         <v>189</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0009207313146293164</v>
+        <v>0.0009095619542784989</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0001807557020159438</v>
+        <v>0.0001767899134187028</v>
       </c>
       <c r="D191" t="n">
-        <v>0.1309803552942276</v>
+        <v>0.1283723564891815</v>
       </c>
       <c r="E191" t="n">
-        <v>8.507384042488411e-05</v>
+        <v>9.091026881569996e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.004875891477349677</v>
+        <v>0.004767930855318223</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0001810382649260322</v>
+        <v>0.0001768706520779292</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1308690400390018</v>
+        <v>0.1283048210301563</v>
       </c>
       <c r="I191" t="n">
-        <v>0.004040507975339792</v>
+        <v>0.003949536095232039</v>
       </c>
     </row>
     <row r="192">
@@ -5990,28 +5990,28 @@
         <v>190</v>
       </c>
       <c r="B192" t="n">
-        <v>0.000921891065210104</v>
+        <v>0.0009089566162079573</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0001808516631666571</v>
+        <v>0.000176827862768434</v>
       </c>
       <c r="D192" t="n">
-        <v>0.1309461009864807</v>
+        <v>0.1283651797590256</v>
       </c>
       <c r="E192" t="n">
-        <v>8.630891788424924e-05</v>
+        <v>9.030286620371043e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.004880144095008807</v>
+        <v>0.004777966891620521</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0001807426763216085</v>
+        <v>0.0001758649409216863</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1309679769040321</v>
+        <v>0.1285074202816016</v>
       </c>
       <c r="I192" t="n">
-        <v>0.004044561471856924</v>
+        <v>0.003959564826683692</v>
       </c>
     </row>
     <row r="193">
@@ -6019,28 +6019,28 @@
         <v>191</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0009208582031205296</v>
+        <v>0.0009086100815422833</v>
       </c>
       <c r="C193" t="n">
-        <v>0.000180680091034621</v>
+        <v>0.0001764505338435993</v>
       </c>
       <c r="D193" t="n">
-        <v>0.1309955246667862</v>
+        <v>0.1284295501451492</v>
       </c>
       <c r="E193" t="n">
-        <v>8.520050885202363e-05</v>
+        <v>9.00118060791865e-05</v>
       </c>
       <c r="F193" t="n">
-        <v>0.00490157962513884</v>
+        <v>0.004781480646687659</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0001808314797133101</v>
+        <v>0.0001764488982906121</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1309002956218082</v>
+        <v>0.1283734932750901</v>
       </c>
       <c r="I193" t="n">
-        <v>0.004066246725606685</v>
+        <v>0.003963164279866374</v>
       </c>
     </row>
     <row r="194">
@@ -6048,28 +6048,28 @@
         <v>192</v>
       </c>
       <c r="B194" t="n">
-        <v>0.0009198755352199078</v>
+        <v>0.0009080789376422763</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0001808769833352417</v>
+        <v>0.0001767858270723373</v>
       </c>
       <c r="D194" t="n">
-        <v>0.1309470308666229</v>
+        <v>0.1283613835601807</v>
       </c>
       <c r="E194" t="n">
-        <v>8.426341702230275e-05</v>
+        <v>8.94862103909254e-05</v>
       </c>
       <c r="F194" t="n">
-        <v>0.004889637867587377</v>
+        <v>0.004772502967410191</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0001806410383704676</v>
+        <v>0.0001762079787590628</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1309548177726895</v>
+        <v>0.128426720102304</v>
       </c>
       <c r="I194" t="n">
-        <v>0.004054222809238933</v>
+        <v>0.003954161383700823</v>
       </c>
     </row>
     <row r="195">
@@ -6077,28 +6077,28 @@
         <v>193</v>
       </c>
       <c r="B195" t="n">
-        <v>0.000920146895531565</v>
+        <v>0.0009079227266646922</v>
       </c>
       <c r="C195" t="n">
-        <v>0.0001805558222243562</v>
+        <v>0.00017639675243292</v>
       </c>
       <c r="D195" t="n">
-        <v>0.1310018795862198</v>
+        <v>0.1284399483699799</v>
       </c>
       <c r="E195" t="n">
-        <v>8.458168325340375e-05</v>
+        <v>8.932624364364892e-05</v>
       </c>
       <c r="F195" t="n">
-        <v>0.004881261524943358</v>
+        <v>0.004774312426048965</v>
       </c>
       <c r="G195" t="n">
-        <v>0.000180510533593753</v>
+        <v>0.0001763707670000675</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1309807030878487</v>
+        <v>0.128394196475894</v>
       </c>
       <c r="I195" t="n">
-        <v>0.004045847489697582</v>
+        <v>0.003955970663534778</v>
       </c>
     </row>
     <row r="196">
@@ -6106,28 +6106,28 @@
         <v>194</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0009199201477207244</v>
+        <v>0.0009064557101987302</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0001805608213255182</v>
+        <v>0.0001763301531355828</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1310010808515549</v>
+        <v>0.1284512788524628</v>
       </c>
       <c r="E196" t="n">
-        <v>8.435392566164956e-05</v>
+        <v>8.786917486740277e-05</v>
       </c>
       <c r="F196" t="n">
-        <v>0.004880795132347533</v>
+        <v>0.004767883759247197</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0001804434870567999</v>
+        <v>0.0001764476393576602</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1309878177073029</v>
+        <v>0.128368696849459</v>
       </c>
       <c r="I196" t="n">
-        <v>0.004045412636272379</v>
+        <v>0.003949592622410245</v>
       </c>
     </row>
     <row r="197">
@@ -6135,28 +6135,28 @@
         <v>195</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0009198553894087672</v>
+        <v>0.0009080246094837784</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0001804754397878423</v>
+        <v>0.0001764831302380189</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1310070100708008</v>
+        <v>0.1284202164936066</v>
       </c>
       <c r="E197" t="n">
-        <v>8.434491189336405e-05</v>
+        <v>8.944041139353066e-05</v>
       </c>
       <c r="F197" t="n">
-        <v>0.004878957944285568</v>
+        <v>0.004776741972323781</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0001804428232710681</v>
+        <v>0.0001763846468570495</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1309792655628618</v>
+        <v>0.1283958909017616</v>
       </c>
       <c r="I197" t="n">
-        <v>0.004043618811759338</v>
+        <v>0.003958377868566072</v>
       </c>
     </row>
     <row r="198">
@@ -6164,28 +6164,28 @@
         <v>196</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0009202212973870337</v>
+        <v>0.0009071419076994062</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0001805727984430268</v>
+        <v>0.0001764523103274405</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1309915536203384</v>
+        <v>0.1284208009319305</v>
       </c>
       <c r="E198" t="n">
-        <v>8.469074273994193e-05</v>
+        <v>8.858561543514952e-05</v>
       </c>
       <c r="F198" t="n">
-        <v>0.004882175094018072</v>
+        <v>0.004766751913730584</v>
       </c>
       <c r="G198" t="n">
-        <v>0.0001804368954636521</v>
+        <v>0.0001765098054936994</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1309814443615482</v>
+        <v>0.1283730099922681</v>
       </c>
       <c r="I198" t="n">
-        <v>0.004046830970499221</v>
+        <v>0.003948377032626001</v>
       </c>
     </row>
     <row r="199">
@@ -6193,28 +6193,28 @@
         <v>197</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0009196092970073223</v>
+        <v>0.000906384613007307</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0001805658663641661</v>
+        <v>0.0001764513130001724</v>
       </c>
       <c r="D199" t="n">
-        <v>0.1310075823059082</v>
+        <v>0.1284200123643875</v>
       </c>
       <c r="E199" t="n">
-        <v>8.400552789960057e-05</v>
+        <v>8.783325878484175e-05</v>
       </c>
       <c r="F199" t="n">
-        <v>0.004880949368496801</v>
+        <v>0.004779269036337077</v>
       </c>
       <c r="G199" t="n">
-        <v>0.000180408928805786</v>
+        <v>0.0001764820189652797</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1309795234010815</v>
+        <v>0.1283797451061292</v>
       </c>
       <c r="I199" t="n">
-        <v>0.00404564283511694</v>
+        <v>0.003960888313120429</v>
       </c>
     </row>
     <row r="200">
@@ -6222,28 +6222,28 @@
         <v>198</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0009191016646847128</v>
+        <v>0.000908110126927495</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0001805465055890381</v>
+        <v>0.0001764706326453015</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1310139395332336</v>
+        <v>0.1284152128810883</v>
       </c>
       <c r="E200" t="n">
-        <v>8.348548114439473e-05</v>
+        <v>8.956343904696405e-05</v>
       </c>
       <c r="F200" t="n">
-        <v>0.004880147456794636</v>
+        <v>0.004772401271664445</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0001804699340997018</v>
+        <v>0.0001764436996248315</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1309745183679447</v>
+        <v>0.1283813844399973</v>
       </c>
       <c r="I200" t="n">
-        <v>0.004044804985028788</v>
+        <v>0.003954050699051402</v>
       </c>
     </row>
     <row r="201">
@@ -6251,28 +6251,28 @@
         <v>199</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0009188637545034289</v>
+        <v>0.000905596421547234</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0001804667585203424</v>
+        <v>0.0001764262217069045</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1310087475748062</v>
+        <v>0.1284179249267578</v>
       </c>
       <c r="E201" t="n">
-        <v>8.33532719835639e-05</v>
+        <v>8.708058573398739e-05</v>
       </c>
       <c r="F201" t="n">
-        <v>0.004885190711531417</v>
+        <v>0.004779337552022098</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0001804930314455458</v>
+        <v>0.0001764523262783982</v>
       </c>
       <c r="H201" t="n">
-        <v>0.130972099773841</v>
+        <v>0.128380926440046</v>
       </c>
       <c r="I201" t="n">
-        <v>0.004049837181700142</v>
+        <v>0.003960980623292009</v>
       </c>
     </row>
   </sheetData>
